--- a/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
+++ b/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
@@ -1957,7 +1957,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -2009,7 +2009,9 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2029,7 +2031,9 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color auto="1"/>
@@ -2144,6 +2148,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -2157,6 +2172,15 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2180,7 +2204,9 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -2206,9 +2232,22 @@
       <left style="medium">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -2241,32 +2280,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2314,7 +2327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2337,6 +2350,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2373,175 +2387,169 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4626,15 +4634,16 @@
     <row r="4" spans="2:22" ht="12.75" customHeight="1">
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="J4" s="10">
+      <c r="E4" s="10"/>
+      <c r="J4" s="11">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
     </row>
     <row r="5" spans="2:22" ht="12" customHeight="1">
       <c r="B5" s="6">
@@ -4642,8 +4651,8 @@
         <v>0</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="11"/>
-      <c r="J5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="6">
@@ -4651,21 +4660,21 @@
         <v>0</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="J7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="J7" s="15"/>
     </row>
     <row r="8" spans="2:22">
       <c r="B8" s="6">
@@ -4673,19 +4682,19 @@
         <v>0</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="15">
+      <c r="D8" s="16">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="15">
+      <c r="E8" s="17"/>
+      <c r="F8" s="16">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="18">
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="19">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>0</v>
       </c>
@@ -4696,2831 +4705,2831 @@
         <v>0</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <f>D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="15">
+      <c r="E9" s="17"/>
+      <c r="F9" s="16">
         <f>F8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="J9" s="19"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="J9" s="20"/>
     </row>
     <row r="11" spans="2:22" ht="13.5" customHeight="1">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="25">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="26">
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="K11" s="25"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="27"/>
-      <c r="Q11" s="25">
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
+      <c r="Q11" s="26">
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="R11" s="25"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="27"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="28"/>
     </row>
     <row r="12" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B12" s="28">
+      <c r="B12" s="29">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="24"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="30"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="30"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="25"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="31"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="31"/>
     </row>
     <row r="13" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="24"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="32">
+      <c r="C13" s="32"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="25"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="33">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="33" t="s">
         <v>447</v>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="33">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="34">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="32">
+      <c r="Q13" s="30"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="33">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="T13" s="32" t="s">
+      <c r="T13" s="33" t="s">
         <v>447</v>
       </c>
-      <c r="U13" s="32">
+      <c r="U13" s="33">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="33">
+      <c r="V13" s="34">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B14" s="31"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="24"/>
-      <c r="J14" s="35" t="s">
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="25"/>
+      <c r="J14" s="37" t="s">
         <v>448</v>
       </c>
-      <c r="K14" s="36">
+      <c r="K14" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L14" s="37"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="39">
+      <c r="L14" s="39"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="35" t="s">
+      <c r="Q14" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="R14" s="36">
+      <c r="R14" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S14" s="37"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="39">
+      <c r="S14" s="39"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="40">
+      <c r="B15" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
-      <c r="J15" s="35" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="46"/>
+      <c r="J15" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L15" s="37"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="39">
+      <c r="L15" s="39"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="35" t="s">
+      <c r="Q15" s="37" t="s">
         <v>451</v>
       </c>
-      <c r="R15" s="36">
+      <c r="R15" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S15" s="37"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="39">
+      <c r="S15" s="39"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B16" s="45">
+      <c r="B16" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="41">
-        <v>0</v>
-      </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="46">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="44"/>
-      <c r="J16" s="35" t="s">
+      <c r="C16" s="47"/>
+      <c r="D16" s="43">
+        <v>0</v>
+      </c>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="48">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="46"/>
+      <c r="J16" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L16" s="37"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="39">
+      <c r="L16" s="39"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="35" t="s">
+      <c r="Q16" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="R16" s="36">
+      <c r="R16" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S16" s="37"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="39">
+      <c r="S16" s="39"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B17" s="45">
+      <c r="B17" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="41">
-        <v>0</v>
-      </c>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="46">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="44"/>
-      <c r="J17" s="35" t="s">
+      <c r="C17" s="47"/>
+      <c r="D17" s="43">
+        <v>0</v>
+      </c>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="48">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="46"/>
+      <c r="J17" s="37" t="s">
         <v>454</v>
       </c>
-      <c r="K17" s="36">
+      <c r="K17" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L17" s="37"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="39">
+      <c r="L17" s="39"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="35" t="s">
+      <c r="Q17" s="37" t="s">
         <v>455</v>
       </c>
-      <c r="R17" s="36">
+      <c r="R17" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S17" s="37"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="39">
+      <c r="S17" s="39"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B18" s="45">
+      <c r="B18" s="47">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="41">
-        <v>0</v>
-      </c>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="46">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="44"/>
-      <c r="J18" s="35" t="s">
+      <c r="C18" s="47"/>
+      <c r="D18" s="43">
+        <v>0</v>
+      </c>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="48">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="46"/>
+      <c r="J18" s="37" t="s">
         <v>456</v>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="37"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="39">
+      <c r="L18" s="39"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="35" t="s">
+      <c r="Q18" s="37" t="s">
         <v>457</v>
       </c>
-      <c r="R18" s="36">
+      <c r="R18" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S18" s="37"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="39">
+      <c r="S18" s="39"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B19" s="47">
+      <c r="B19" s="49">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="41">
-        <v>0</v>
-      </c>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="46">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="44"/>
-      <c r="J19" s="35" t="s">
+      <c r="C19" s="49"/>
+      <c r="D19" s="43">
+        <v>0</v>
+      </c>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="48">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="46"/>
+      <c r="J19" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="K19" s="36">
+      <c r="K19" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L19" s="37"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="39">
+      <c r="L19" s="39"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="35" t="s">
+      <c r="Q19" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="R19" s="36">
+      <c r="R19" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S19" s="37"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="39">
+      <c r="S19" s="39"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B20" s="48">
+      <c r="B20" s="50">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C20" s="48"/>
-      <c r="D20" s="49">
+      <c r="C20" s="50"/>
+      <c r="D20" s="51">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="51">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="51">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="50">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="51"/>
-      <c r="J20" s="35" t="s">
+      <c r="G20" s="52">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="53"/>
+      <c r="J20" s="37" t="s">
         <v>460</v>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L20" s="37"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="39">
+      <c r="L20" s="39"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="35" t="s">
+      <c r="Q20" s="37" t="s">
         <v>461</v>
       </c>
-      <c r="R20" s="36">
+      <c r="R20" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S20" s="37"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="39">
+      <c r="S20" s="39"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+      <c r="V20" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="13.5" customHeight="1">
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="37" t="s">
         <v>462</v>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L21" s="37"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="39">
+      <c r="L21" s="39"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="35" t="s">
+      <c r="Q21" s="37" t="s">
         <v>463</v>
       </c>
-      <c r="R21" s="36">
+      <c r="R21" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S21" s="37"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="39">
+      <c r="S21" s="39"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:22">
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="37" t="s">
         <v>464</v>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L22" s="37"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="39">
+      <c r="L22" s="39"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="35" t="s">
+      <c r="Q22" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="R22" s="36">
+      <c r="R22" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S22" s="37"/>
-      <c r="T22" s="38"/>
-      <c r="U22" s="38"/>
-      <c r="V22" s="39">
+      <c r="S22" s="39"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:22" ht="13.5" customHeight="1">
-      <c r="B23" s="20"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="52">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23">
         <f>D11</f>
         <v>0</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,25,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="52">
+      <c r="F23" s="23">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,55,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G23" s="23">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,56,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="54">
+      <c r="H23" s="25">
         <f>H11</f>
         <v>0</v>
       </c>
-      <c r="J23" s="35" t="s">
+      <c r="J23" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="37"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="39">
+      <c r="L23" s="39"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="35" t="s">
+      <c r="Q23" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="R23" s="36">
+      <c r="R23" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S23" s="37"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="39">
+      <c r="S23" s="39"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B24" s="28">
+      <c r="B24" s="29">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,24,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="54"/>
-      <c r="J24" s="35" t="s">
+      <c r="C24" s="29"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="25"/>
+      <c r="J24" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L24" s="37"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="39">
+      <c r="L24" s="39"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="35" t="s">
+      <c r="Q24" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="R24" s="36">
+      <c r="R24" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S24" s="37"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="39">
+      <c r="S24" s="39"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <f>B13</f>
         <v>0</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="54"/>
-      <c r="J25" s="35" t="s">
+      <c r="C25" s="32"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="25"/>
+      <c r="J25" s="37" t="s">
         <v>470</v>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L25" s="37"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="39">
+      <c r="L25" s="39"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="35" t="s">
+      <c r="Q25" s="37" t="s">
         <v>471</v>
       </c>
-      <c r="R25" s="36">
+      <c r="R25" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S25" s="37"/>
-      <c r="T25" s="38"/>
-      <c r="U25" s="38"/>
-      <c r="V25" s="39">
+      <c r="S25" s="39"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B26" s="31"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="54"/>
-      <c r="J26" s="35" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="25"/>
+      <c r="J26" s="37" t="s">
         <v>472</v>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="37"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="39">
+      <c r="L26" s="39"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="35" t="s">
+      <c r="Q26" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="R26" s="36">
+      <c r="R26" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S26" s="37"/>
-      <c r="T26" s="38"/>
-      <c r="U26" s="38"/>
-      <c r="V26" s="39">
+      <c r="S26" s="39"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="56" t="s">
         <v>474</v>
       </c>
-      <c r="C27" s="58" t="str">
+      <c r="C27" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,29,FALSE))</f>
         <v/>
       </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="61"/>
-      <c r="J27" s="35" t="s">
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
+      <c r="J27" s="37" t="s">
         <v>475</v>
       </c>
-      <c r="K27" s="36">
+      <c r="K27" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L27" s="37"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="39">
+      <c r="L27" s="39"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="35" t="s">
+      <c r="Q27" s="37" t="s">
         <v>476</v>
       </c>
-      <c r="R27" s="36">
+      <c r="R27" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S27" s="37"/>
-      <c r="T27" s="38"/>
-      <c r="U27" s="38"/>
-      <c r="V27" s="39">
+      <c r="S27" s="39"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:22">
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="61" t="s">
         <v>477</v>
       </c>
-      <c r="C28" s="63"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="68"/>
-      <c r="J28" s="35" t="s">
+      <c r="C28" s="62"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="67"/>
+      <c r="J28" s="37" t="s">
         <v>478</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="37"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="39">
+      <c r="L28" s="39"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="35" t="s">
+      <c r="Q28" s="37" t="s">
         <v>479</v>
       </c>
-      <c r="R28" s="36">
+      <c r="R28" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S28" s="37"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="38"/>
-      <c r="V28" s="39">
+      <c r="S28" s="39"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="40"/>
+      <c r="V28" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:22">
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="61" t="s">
         <v>480</v>
       </c>
-      <c r="C29" s="63"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="68"/>
-      <c r="J29" s="35" t="s">
+      <c r="C29" s="62"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="67"/>
+      <c r="J29" s="37" t="s">
         <v>481</v>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L29" s="37"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="39">
+      <c r="L29" s="39"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="35" t="s">
+      <c r="Q29" s="37" t="s">
         <v>482</v>
       </c>
-      <c r="R29" s="36">
+      <c r="R29" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S29" s="37"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="38"/>
-      <c r="V29" s="39">
+      <c r="S29" s="39"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:22">
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="61" t="s">
         <v>483</v>
       </c>
-      <c r="C30" s="63"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H30" s="68"/>
-      <c r="J30" s="35" t="s">
+      <c r="C30" s="62"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="67"/>
+      <c r="J30" s="37" t="s">
         <v>484</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L30" s="37"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="39">
+      <c r="L30" s="39"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="35" t="s">
+      <c r="Q30" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="38">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S30" s="37"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="39">
+      <c r="S30" s="39"/>
+      <c r="T30" s="40"/>
+      <c r="U30" s="40"/>
+      <c r="V30" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:22">
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="61" t="s">
         <v>486</v>
       </c>
-      <c r="C31" s="63"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H31" s="68"/>
-      <c r="J31" s="55" t="s">
+      <c r="C31" s="62"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="67"/>
+      <c r="J31" s="54" t="s">
         <v>487</v>
       </c>
-      <c r="K31" s="56">
+      <c r="K31" s="55">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="37"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="39">
+      <c r="L31" s="39"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="41">
         <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="55" t="s">
+      <c r="Q31" s="54" t="s">
         <v>488</v>
       </c>
-      <c r="R31" s="56">
+      <c r="R31" s="55">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S31" s="37"/>
-      <c r="T31" s="38"/>
-      <c r="U31" s="38"/>
-      <c r="V31" s="39">
+      <c r="S31" s="39"/>
+      <c r="T31" s="40"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="41">
         <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:22">
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="61" t="s">
         <v>489</v>
       </c>
-      <c r="C32" s="63"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H32" s="68"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="67"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="61" t="s">
         <v>490</v>
       </c>
-      <c r="C33" s="63"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H33" s="68"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="67"/>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="62" t="s">
+      <c r="B34" s="61" t="s">
         <v>491</v>
       </c>
-      <c r="C34" s="63"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H34" s="68"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="67"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="62" t="s">
+      <c r="B35" s="61" t="s">
         <v>492</v>
       </c>
-      <c r="C35" s="63"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H35" s="68"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="67"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="61" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="63"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H36" s="68"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H36" s="67"/>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="62" t="s">
+      <c r="B37" s="61" t="s">
         <v>494</v>
       </c>
-      <c r="C37" s="63"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H37" s="68"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="67"/>
     </row>
     <row r="38" spans="2:8">
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="61" t="s">
         <v>495</v>
       </c>
-      <c r="C38" s="63"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H38" s="68"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="67"/>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="61" t="s">
         <v>496</v>
       </c>
-      <c r="C39" s="63"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H39" s="68"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="67"/>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="62" t="s">
+      <c r="B40" s="61" t="s">
         <v>497</v>
       </c>
-      <c r="C40" s="63"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H40" s="68"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H40" s="67"/>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="61" t="s">
         <v>498</v>
       </c>
-      <c r="C41" s="63"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H41" s="68"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H41" s="67"/>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="61" t="s">
         <v>499</v>
       </c>
-      <c r="C42" s="63"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H42" s="68"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H42" s="67"/>
     </row>
     <row r="43" spans="2:8">
-      <c r="B43" s="62" t="s">
+      <c r="B43" s="61" t="s">
         <v>500</v>
       </c>
-      <c r="C43" s="63"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H43" s="68"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H43" s="67"/>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="62" t="s">
+      <c r="B44" s="61" t="s">
         <v>501</v>
       </c>
-      <c r="C44" s="63"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="66"/>
-      <c r="G44" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H44" s="68"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H44" s="67"/>
     </row>
     <row r="45" spans="2:8">
-      <c r="B45" s="62" t="s">
+      <c r="B45" s="61" t="s">
         <v>502</v>
       </c>
-      <c r="C45" s="63"/>
-      <c r="D45" s="64"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="66"/>
-      <c r="G45" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H45" s="68"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="67"/>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="62" t="s">
+      <c r="B46" s="61" t="s">
         <v>503</v>
       </c>
-      <c r="C46" s="63"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="66"/>
-      <c r="G46" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H46" s="68"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H46" s="67"/>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="62" t="s">
+      <c r="B47" s="61" t="s">
         <v>504</v>
       </c>
-      <c r="C47" s="63"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H47" s="68"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="64"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H47" s="67"/>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="69" t="str">
+      <c r="B48" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,30,FALSE))</f>
         <v/>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="71" t="str">
-        <f t="array" ref="D48">SUMPRODUCT(ROUND(D28:D47,2))</f>
-        <v/>
-      </c>
-      <c r="E48" s="71" t="str">
-        <f t="array" ref="E48">SUMPRODUCT(ROUND(E28:E47,2))</f>
-        <v/>
-      </c>
-      <c r="F48" s="71" t="str">
-        <f t="array" ref="F48">SUMPRODUCT(ROUND(F28:F47,2))</f>
-        <v/>
-      </c>
-      <c r="G48" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H48" s="73"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(D28:D47,2))</f>
+        <v/>
+      </c>
+      <c r="E48" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(E28:E47,2))</f>
+        <v/>
+      </c>
+      <c r="F48" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(F28:F47,2))</f>
+        <v/>
+      </c>
+      <c r="G48" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="72"/>
     </row>
     <row r="49" spans="2:8">
-      <c r="B49" s="57" t="s">
+      <c r="B49" s="56" t="s">
         <v>505</v>
       </c>
-      <c r="C49" s="58" t="str">
+      <c r="C49" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,31,FALSE))</f>
         <v/>
       </c>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="60"/>
-      <c r="H49" s="61"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="60"/>
     </row>
     <row r="50" spans="2:8">
-      <c r="B50" s="62" t="s">
+      <c r="B50" s="61" t="s">
         <v>506</v>
       </c>
-      <c r="C50" s="63"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="66"/>
-      <c r="G50" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H50" s="68"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="64"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H50" s="67"/>
     </row>
     <row r="51" spans="2:8">
-      <c r="B51" s="62" t="s">
+      <c r="B51" s="61" t="s">
         <v>507</v>
       </c>
-      <c r="C51" s="63"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="66"/>
-      <c r="G51" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H51" s="68"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="64"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H51" s="67"/>
     </row>
     <row r="52" spans="2:8">
-      <c r="B52" s="62" t="s">
+      <c r="B52" s="61" t="s">
         <v>508</v>
       </c>
-      <c r="C52" s="63"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H52" s="68"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H52" s="67"/>
     </row>
     <row r="53" spans="2:8">
-      <c r="B53" s="62" t="s">
+      <c r="B53" s="61" t="s">
         <v>509</v>
       </c>
-      <c r="C53" s="63"/>
-      <c r="D53" s="64"/>
-      <c r="E53" s="65"/>
-      <c r="F53" s="66"/>
-      <c r="G53" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H53" s="68"/>
+      <c r="C53" s="62"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="64"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H53" s="67"/>
     </row>
     <row r="54" spans="2:8">
-      <c r="B54" s="62" t="s">
+      <c r="B54" s="61" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="63"/>
-      <c r="D54" s="64"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="66"/>
-      <c r="G54" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H54" s="68"/>
+      <c r="C54" s="62"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H54" s="67"/>
     </row>
     <row r="55" spans="2:8">
-      <c r="B55" s="62" t="s">
+      <c r="B55" s="61" t="s">
         <v>511</v>
       </c>
-      <c r="C55" s="63"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="65"/>
-      <c r="F55" s="66"/>
-      <c r="G55" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H55" s="68"/>
+      <c r="C55" s="62"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H55" s="67"/>
     </row>
     <row r="56" spans="2:8">
-      <c r="B56" s="62" t="s">
+      <c r="B56" s="61" t="s">
         <v>512</v>
       </c>
-      <c r="C56" s="63"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H56" s="68"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H56" s="67"/>
     </row>
     <row r="57" spans="2:8">
-      <c r="B57" s="62" t="s">
+      <c r="B57" s="61" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="63"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="65"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H57" s="68"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H57" s="67"/>
     </row>
     <row r="58" spans="2:8">
-      <c r="B58" s="62" t="s">
+      <c r="B58" s="61" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="63"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="66"/>
-      <c r="G58" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H58" s="68"/>
+      <c r="C58" s="62"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H58" s="67"/>
     </row>
     <row r="59" spans="2:8">
-      <c r="B59" s="62" t="s">
+      <c r="B59" s="61" t="s">
         <v>515</v>
       </c>
-      <c r="C59" s="63"/>
-      <c r="D59" s="64"/>
-      <c r="E59" s="65"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H59" s="68"/>
+      <c r="C59" s="62"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="64"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H59" s="67"/>
     </row>
     <row r="60" spans="2:8">
-      <c r="B60" s="62" t="s">
+      <c r="B60" s="61" t="s">
         <v>516</v>
       </c>
-      <c r="C60" s="63"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="65"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H60" s="68"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="64"/>
+      <c r="F60" s="65"/>
+      <c r="G60" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H60" s="67"/>
     </row>
     <row r="61" spans="2:8">
-      <c r="B61" s="62" t="s">
+      <c r="B61" s="61" t="s">
         <v>517</v>
       </c>
-      <c r="C61" s="63"/>
-      <c r="D61" s="64"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="66"/>
-      <c r="G61" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H61" s="68"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="64"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H61" s="67"/>
     </row>
     <row r="62" spans="2:8">
-      <c r="B62" s="62" t="s">
+      <c r="B62" s="61" t="s">
         <v>518</v>
       </c>
-      <c r="C62" s="63"/>
-      <c r="D62" s="64"/>
-      <c r="E62" s="65"/>
-      <c r="F62" s="66"/>
-      <c r="G62" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H62" s="68"/>
+      <c r="C62" s="62"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="65"/>
+      <c r="G62" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H62" s="67"/>
     </row>
     <row r="63" spans="2:8">
-      <c r="B63" s="62" t="s">
+      <c r="B63" s="61" t="s">
         <v>519</v>
       </c>
-      <c r="C63" s="63"/>
-      <c r="D63" s="64"/>
-      <c r="E63" s="65"/>
-      <c r="F63" s="66"/>
-      <c r="G63" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H63" s="68"/>
+      <c r="C63" s="62"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H63" s="67"/>
     </row>
     <row r="64" spans="2:8">
-      <c r="B64" s="62" t="s">
+      <c r="B64" s="61" t="s">
         <v>520</v>
       </c>
-      <c r="C64" s="63"/>
-      <c r="D64" s="64"/>
-      <c r="E64" s="65"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H64" s="68"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="64"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H64" s="67"/>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="62" t="s">
+      <c r="B65" s="61" t="s">
         <v>521</v>
       </c>
-      <c r="C65" s="63"/>
-      <c r="D65" s="64"/>
-      <c r="E65" s="65"/>
-      <c r="F65" s="66"/>
-      <c r="G65" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H65" s="68"/>
+      <c r="C65" s="62"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="64"/>
+      <c r="F65" s="65"/>
+      <c r="G65" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H65" s="67"/>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="62" t="s">
+      <c r="B66" s="61" t="s">
         <v>522</v>
       </c>
-      <c r="C66" s="63"/>
-      <c r="D66" s="64"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="66"/>
-      <c r="G66" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H66" s="68"/>
+      <c r="C66" s="62"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H66" s="67"/>
     </row>
     <row r="67" spans="2:8">
-      <c r="B67" s="62" t="s">
+      <c r="B67" s="61" t="s">
         <v>523</v>
       </c>
-      <c r="C67" s="63"/>
-      <c r="D67" s="64"/>
-      <c r="E67" s="65"/>
-      <c r="F67" s="66"/>
-      <c r="G67" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H67" s="68"/>
+      <c r="C67" s="62"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="64"/>
+      <c r="F67" s="65"/>
+      <c r="G67" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H67" s="67"/>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="62" t="s">
+      <c r="B68" s="61" t="s">
         <v>524</v>
       </c>
-      <c r="C68" s="63"/>
-      <c r="D68" s="64"/>
-      <c r="E68" s="65"/>
-      <c r="F68" s="66"/>
-      <c r="G68" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H68" s="68"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="64"/>
+      <c r="F68" s="65"/>
+      <c r="G68" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H68" s="67"/>
     </row>
     <row r="69" spans="2:8">
-      <c r="B69" s="62" t="s">
+      <c r="B69" s="61" t="s">
         <v>525</v>
       </c>
-      <c r="C69" s="63"/>
-      <c r="D69" s="64"/>
-      <c r="E69" s="65"/>
-      <c r="F69" s="66"/>
-      <c r="G69" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H69" s="68"/>
+      <c r="C69" s="62"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="65"/>
+      <c r="G69" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H69" s="67"/>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="69" t="str">
+      <c r="B70" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,32,FALSE))</f>
         <v/>
       </c>
-      <c r="C70" s="70"/>
-      <c r="D70" s="71" t="str">
-        <f t="array" ref="D70">SUMPRODUCT(ROUND(D50:D69,2))</f>
-        <v/>
-      </c>
-      <c r="E70" s="71" t="str">
-        <f t="array" ref="E70">SUMPRODUCT(ROUND(E50:E69,2))</f>
-        <v/>
-      </c>
-      <c r="F70" s="71" t="str">
-        <f t="array" ref="F70">SUMPRODUCT(ROUND(F50:F69,2))</f>
-        <v/>
-      </c>
-      <c r="G70" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H70" s="73"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(D50:D69,2))</f>
+        <v/>
+      </c>
+      <c r="E70" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(E50:E69,2))</f>
+        <v/>
+      </c>
+      <c r="F70" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(F50:F69,2))</f>
+        <v/>
+      </c>
+      <c r="G70" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H70" s="72"/>
     </row>
     <row r="71" spans="2:8">
-      <c r="B71" s="57" t="s">
+      <c r="B71" s="56" t="s">
         <v>526</v>
       </c>
-      <c r="C71" s="58" t="str">
+      <c r="C71" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,33,FALSE))</f>
         <v/>
       </c>
-      <c r="D71" s="59"/>
-      <c r="E71" s="59"/>
-      <c r="F71" s="59"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="61"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="59"/>
+      <c r="H71" s="60"/>
     </row>
     <row r="72" spans="2:8">
-      <c r="B72" s="62" t="s">
+      <c r="B72" s="61" t="s">
         <v>527</v>
       </c>
-      <c r="C72" s="63"/>
-      <c r="D72" s="64"/>
-      <c r="E72" s="65"/>
-      <c r="F72" s="66"/>
-      <c r="G72" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H72" s="68"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="64"/>
+      <c r="F72" s="65"/>
+      <c r="G72" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H72" s="67"/>
     </row>
     <row r="73" spans="2:8">
-      <c r="B73" s="62" t="s">
+      <c r="B73" s="61" t="s">
         <v>528</v>
       </c>
-      <c r="C73" s="63"/>
-      <c r="D73" s="64"/>
-      <c r="E73" s="65"/>
-      <c r="F73" s="66"/>
-      <c r="G73" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H73" s="68"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="64"/>
+      <c r="F73" s="65"/>
+      <c r="G73" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H73" s="67"/>
     </row>
     <row r="74" spans="2:8">
-      <c r="B74" s="62" t="s">
+      <c r="B74" s="61" t="s">
         <v>529</v>
       </c>
-      <c r="C74" s="63"/>
-      <c r="D74" s="64"/>
-      <c r="E74" s="65"/>
-      <c r="F74" s="66"/>
-      <c r="G74" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H74" s="68"/>
+      <c r="C74" s="62"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="64"/>
+      <c r="F74" s="65"/>
+      <c r="G74" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H74" s="67"/>
     </row>
     <row r="75" spans="2:8">
-      <c r="B75" s="62" t="s">
+      <c r="B75" s="61" t="s">
         <v>530</v>
       </c>
-      <c r="C75" s="63"/>
-      <c r="D75" s="64"/>
-      <c r="E75" s="65"/>
-      <c r="F75" s="66"/>
-      <c r="G75" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H75" s="68"/>
+      <c r="C75" s="62"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="64"/>
+      <c r="F75" s="65"/>
+      <c r="G75" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H75" s="67"/>
     </row>
     <row r="76" spans="2:8">
-      <c r="B76" s="62" t="s">
+      <c r="B76" s="61" t="s">
         <v>531</v>
       </c>
-      <c r="C76" s="63"/>
-      <c r="D76" s="64"/>
-      <c r="E76" s="65"/>
-      <c r="F76" s="66"/>
-      <c r="G76" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H76" s="68"/>
+      <c r="C76" s="62"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="64"/>
+      <c r="F76" s="65"/>
+      <c r="G76" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H76" s="67"/>
     </row>
     <row r="77" spans="2:8">
-      <c r="B77" s="62" t="s">
+      <c r="B77" s="61" t="s">
         <v>532</v>
       </c>
-      <c r="C77" s="63"/>
-      <c r="D77" s="64"/>
-      <c r="E77" s="65"/>
-      <c r="F77" s="66"/>
-      <c r="G77" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H77" s="68"/>
+      <c r="C77" s="62"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="65"/>
+      <c r="G77" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H77" s="67"/>
     </row>
     <row r="78" spans="2:8">
-      <c r="B78" s="62" t="s">
+      <c r="B78" s="61" t="s">
         <v>533</v>
       </c>
-      <c r="C78" s="63"/>
-      <c r="D78" s="64"/>
-      <c r="E78" s="65"/>
-      <c r="F78" s="66"/>
-      <c r="G78" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H78" s="68"/>
+      <c r="C78" s="62"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H78" s="67"/>
     </row>
     <row r="79" spans="2:8">
-      <c r="B79" s="62" t="s">
+      <c r="B79" s="61" t="s">
         <v>534</v>
       </c>
-      <c r="C79" s="63"/>
-      <c r="D79" s="64"/>
-      <c r="E79" s="65"/>
-      <c r="F79" s="66"/>
-      <c r="G79" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H79" s="68"/>
+      <c r="C79" s="62"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="65"/>
+      <c r="G79" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H79" s="67"/>
     </row>
     <row r="80" spans="2:8">
-      <c r="B80" s="62" t="s">
+      <c r="B80" s="61" t="s">
         <v>535</v>
       </c>
-      <c r="C80" s="63"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H80" s="68"/>
+      <c r="C80" s="62"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H80" s="67"/>
     </row>
     <row r="81" spans="2:8">
-      <c r="B81" s="62" t="s">
+      <c r="B81" s="61" t="s">
         <v>536</v>
       </c>
-      <c r="C81" s="63"/>
-      <c r="D81" s="64"/>
-      <c r="E81" s="65"/>
-      <c r="F81" s="66"/>
-      <c r="G81" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H81" s="68"/>
+      <c r="C81" s="62"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="64"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H81" s="67"/>
     </row>
     <row r="82" spans="2:8">
-      <c r="B82" s="62" t="s">
+      <c r="B82" s="61" t="s">
         <v>537</v>
       </c>
-      <c r="C82" s="63"/>
-      <c r="D82" s="64"/>
-      <c r="E82" s="65"/>
-      <c r="F82" s="66"/>
-      <c r="G82" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H82" s="68"/>
+      <c r="C82" s="62"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="64"/>
+      <c r="F82" s="65"/>
+      <c r="G82" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H82" s="67"/>
     </row>
     <row r="83" spans="2:8">
-      <c r="B83" s="62" t="s">
+      <c r="B83" s="61" t="s">
         <v>538</v>
       </c>
-      <c r="C83" s="63"/>
-      <c r="D83" s="64"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="66"/>
-      <c r="G83" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H83" s="68"/>
+      <c r="C83" s="62"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="64"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H83" s="67"/>
     </row>
     <row r="84" spans="2:8">
-      <c r="B84" s="62" t="s">
+      <c r="B84" s="61" t="s">
         <v>539</v>
       </c>
-      <c r="C84" s="63"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="65"/>
-      <c r="F84" s="66"/>
-      <c r="G84" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H84" s="68"/>
+      <c r="C84" s="62"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="65"/>
+      <c r="G84" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H84" s="67"/>
     </row>
     <row r="85" spans="2:8">
-      <c r="B85" s="62" t="s">
+      <c r="B85" s="61" t="s">
         <v>540</v>
       </c>
-      <c r="C85" s="63"/>
-      <c r="D85" s="64"/>
-      <c r="E85" s="65"/>
-      <c r="F85" s="66"/>
-      <c r="G85" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H85" s="68"/>
+      <c r="C85" s="62"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="64"/>
+      <c r="F85" s="65"/>
+      <c r="G85" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H85" s="67"/>
     </row>
     <row r="86" spans="2:8">
-      <c r="B86" s="62" t="s">
+      <c r="B86" s="61" t="s">
         <v>541</v>
       </c>
-      <c r="C86" s="63"/>
-      <c r="D86" s="64"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="66"/>
-      <c r="G86" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H86" s="68"/>
+      <c r="C86" s="62"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="64"/>
+      <c r="F86" s="65"/>
+      <c r="G86" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H86" s="67"/>
     </row>
     <row r="87" spans="2:8">
-      <c r="B87" s="62" t="s">
+      <c r="B87" s="61" t="s">
         <v>542</v>
       </c>
-      <c r="C87" s="63"/>
-      <c r="D87" s="64"/>
-      <c r="E87" s="65"/>
-      <c r="F87" s="66"/>
-      <c r="G87" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H87" s="68"/>
+      <c r="C87" s="62"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="64"/>
+      <c r="F87" s="65"/>
+      <c r="G87" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H87" s="67"/>
     </row>
     <row r="88" spans="2:8">
-      <c r="B88" s="62" t="s">
+      <c r="B88" s="61" t="s">
         <v>543</v>
       </c>
-      <c r="C88" s="63"/>
-      <c r="D88" s="64"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="66"/>
-      <c r="G88" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H88" s="68"/>
+      <c r="C88" s="62"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="64"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H88" s="67"/>
     </row>
     <row r="89" spans="2:8">
-      <c r="B89" s="62" t="s">
+      <c r="B89" s="61" t="s">
         <v>544</v>
       </c>
-      <c r="C89" s="63"/>
-      <c r="D89" s="64"/>
-      <c r="E89" s="65"/>
-      <c r="F89" s="66"/>
-      <c r="G89" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H89" s="68"/>
+      <c r="C89" s="62"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="64"/>
+      <c r="F89" s="65"/>
+      <c r="G89" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H89" s="67"/>
     </row>
     <row r="90" spans="2:8">
-      <c r="B90" s="62" t="s">
+      <c r="B90" s="61" t="s">
         <v>545</v>
       </c>
-      <c r="C90" s="63"/>
-      <c r="D90" s="64"/>
-      <c r="E90" s="65"/>
-      <c r="F90" s="66"/>
-      <c r="G90" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H90" s="68"/>
+      <c r="C90" s="62"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="64"/>
+      <c r="F90" s="65"/>
+      <c r="G90" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H90" s="67"/>
     </row>
     <row r="91" spans="2:8">
-      <c r="B91" s="62" t="s">
+      <c r="B91" s="61" t="s">
         <v>546</v>
       </c>
-      <c r="C91" s="63"/>
-      <c r="D91" s="64"/>
-      <c r="E91" s="65"/>
-      <c r="F91" s="66"/>
-      <c r="G91" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H91" s="68"/>
+      <c r="C91" s="62"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="64"/>
+      <c r="F91" s="65"/>
+      <c r="G91" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H91" s="67"/>
     </row>
     <row r="92" spans="2:8">
-      <c r="B92" s="62" t="s">
+      <c r="B92" s="61" t="s">
         <v>547</v>
       </c>
-      <c r="C92" s="63"/>
-      <c r="D92" s="64"/>
-      <c r="E92" s="65"/>
-      <c r="F92" s="66"/>
-      <c r="G92" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H92" s="68"/>
+      <c r="C92" s="62"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="64"/>
+      <c r="F92" s="65"/>
+      <c r="G92" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H92" s="67"/>
     </row>
     <row r="93" spans="2:8">
-      <c r="B93" s="62" t="s">
+      <c r="B93" s="61" t="s">
         <v>548</v>
       </c>
-      <c r="C93" s="63"/>
-      <c r="D93" s="64"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="66"/>
-      <c r="G93" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H93" s="68"/>
+      <c r="C93" s="62"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="64"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H93" s="67"/>
     </row>
     <row r="94" spans="2:8">
-      <c r="B94" s="62" t="s">
+      <c r="B94" s="61" t="s">
         <v>549</v>
       </c>
-      <c r="C94" s="63"/>
-      <c r="D94" s="64"/>
-      <c r="E94" s="65"/>
-      <c r="F94" s="66"/>
-      <c r="G94" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H94" s="68"/>
+      <c r="C94" s="62"/>
+      <c r="D94" s="63"/>
+      <c r="E94" s="64"/>
+      <c r="F94" s="65"/>
+      <c r="G94" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H94" s="67"/>
     </row>
     <row r="95" spans="2:8">
-      <c r="B95" s="62" t="s">
+      <c r="B95" s="61" t="s">
         <v>550</v>
       </c>
-      <c r="C95" s="63"/>
-      <c r="D95" s="64"/>
-      <c r="E95" s="65"/>
-      <c r="F95" s="66"/>
-      <c r="G95" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H95" s="68"/>
+      <c r="C95" s="62"/>
+      <c r="D95" s="63"/>
+      <c r="E95" s="64"/>
+      <c r="F95" s="65"/>
+      <c r="G95" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H95" s="67"/>
     </row>
     <row r="96" spans="2:8">
-      <c r="B96" s="62" t="s">
+      <c r="B96" s="61" t="s">
         <v>551</v>
       </c>
-      <c r="C96" s="63"/>
-      <c r="D96" s="64"/>
-      <c r="E96" s="65"/>
-      <c r="F96" s="66"/>
-      <c r="G96" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H96" s="68"/>
+      <c r="C96" s="62"/>
+      <c r="D96" s="63"/>
+      <c r="E96" s="64"/>
+      <c r="F96" s="65"/>
+      <c r="G96" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H96" s="67"/>
     </row>
     <row r="97" spans="2:8">
-      <c r="B97" s="62" t="s">
+      <c r="B97" s="61" t="s">
         <v>552</v>
       </c>
-      <c r="C97" s="63"/>
-      <c r="D97" s="64"/>
-      <c r="E97" s="65"/>
-      <c r="F97" s="66"/>
-      <c r="G97" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H97" s="68"/>
+      <c r="C97" s="62"/>
+      <c r="D97" s="63"/>
+      <c r="E97" s="64"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H97" s="67"/>
     </row>
     <row r="98" spans="2:8">
-      <c r="B98" s="62" t="s">
+      <c r="B98" s="61" t="s">
         <v>553</v>
       </c>
-      <c r="C98" s="63"/>
-      <c r="D98" s="64"/>
-      <c r="E98" s="65"/>
-      <c r="F98" s="66"/>
-      <c r="G98" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H98" s="68"/>
+      <c r="C98" s="62"/>
+      <c r="D98" s="63"/>
+      <c r="E98" s="64"/>
+      <c r="F98" s="65"/>
+      <c r="G98" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H98" s="67"/>
     </row>
     <row r="99" spans="2:8">
-      <c r="B99" s="62" t="s">
+      <c r="B99" s="61" t="s">
         <v>554</v>
       </c>
-      <c r="C99" s="63"/>
-      <c r="D99" s="64"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H99" s="68"/>
+      <c r="C99" s="62"/>
+      <c r="D99" s="63"/>
+      <c r="E99" s="64"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H99" s="67"/>
     </row>
     <row r="100" spans="2:8">
-      <c r="B100" s="62" t="s">
+      <c r="B100" s="61" t="s">
         <v>555</v>
       </c>
-      <c r="C100" s="63"/>
-      <c r="D100" s="64"/>
-      <c r="E100" s="65"/>
-      <c r="F100" s="66"/>
-      <c r="G100" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H100" s="68"/>
+      <c r="C100" s="62"/>
+      <c r="D100" s="63"/>
+      <c r="E100" s="64"/>
+      <c r="F100" s="65"/>
+      <c r="G100" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H100" s="67"/>
     </row>
     <row r="101" spans="2:8">
-      <c r="B101" s="62" t="s">
+      <c r="B101" s="61" t="s">
         <v>556</v>
       </c>
-      <c r="C101" s="63"/>
-      <c r="D101" s="64"/>
-      <c r="E101" s="65"/>
-      <c r="F101" s="66"/>
-      <c r="G101" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H101" s="68"/>
+      <c r="C101" s="62"/>
+      <c r="D101" s="63"/>
+      <c r="E101" s="64"/>
+      <c r="F101" s="65"/>
+      <c r="G101" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H101" s="67"/>
     </row>
     <row r="102" spans="2:8">
-      <c r="B102" s="69" t="str">
+      <c r="B102" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,34,FALSE))</f>
         <v/>
       </c>
-      <c r="C102" s="70"/>
-      <c r="D102" s="71" t="str">
-        <f t="array" ref="D102">SUMPRODUCT(ROUND(D72:D101,2))</f>
-        <v/>
-      </c>
-      <c r="E102" s="71" t="str">
-        <f t="array" ref="E102">SUMPRODUCT(ROUND(E72:E101,2))</f>
-        <v/>
-      </c>
-      <c r="F102" s="71" t="str">
-        <f t="array" ref="F102">SUMPRODUCT(ROUND(F72:F101,2))</f>
-        <v/>
-      </c>
-      <c r="G102" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H102" s="73"/>
+      <c r="C102" s="69"/>
+      <c r="D102" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(D72:D101,2))</f>
+        <v/>
+      </c>
+      <c r="E102" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(E72:E101,2))</f>
+        <v/>
+      </c>
+      <c r="F102" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(F72:F101,2))</f>
+        <v/>
+      </c>
+      <c r="G102" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H102" s="72"/>
     </row>
     <row r="103" spans="2:8">
-      <c r="B103" s="57" t="s">
+      <c r="B103" s="56" t="s">
         <v>557</v>
       </c>
-      <c r="C103" s="58" t="str">
+      <c r="C103" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,35,FALSE))</f>
         <v/>
       </c>
-      <c r="D103" s="59"/>
-      <c r="E103" s="59"/>
-      <c r="F103" s="59"/>
-      <c r="G103" s="60"/>
-      <c r="H103" s="61"/>
+      <c r="D103" s="58"/>
+      <c r="E103" s="58"/>
+      <c r="F103" s="58"/>
+      <c r="G103" s="59"/>
+      <c r="H103" s="60"/>
     </row>
     <row r="104" spans="2:8">
-      <c r="B104" s="62" t="s">
+      <c r="B104" s="61" t="s">
         <v>558</v>
       </c>
-      <c r="C104" s="63"/>
-      <c r="D104" s="64"/>
-      <c r="E104" s="65"/>
-      <c r="F104" s="66"/>
-      <c r="G104" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H104" s="68"/>
+      <c r="C104" s="62"/>
+      <c r="D104" s="63"/>
+      <c r="E104" s="64"/>
+      <c r="F104" s="65"/>
+      <c r="G104" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H104" s="67"/>
     </row>
     <row r="105" spans="2:8">
-      <c r="B105" s="62" t="s">
+      <c r="B105" s="61" t="s">
         <v>559</v>
       </c>
-      <c r="C105" s="63"/>
-      <c r="D105" s="64"/>
-      <c r="E105" s="65"/>
-      <c r="F105" s="66"/>
-      <c r="G105" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H105" s="68"/>
+      <c r="C105" s="62"/>
+      <c r="D105" s="63"/>
+      <c r="E105" s="64"/>
+      <c r="F105" s="65"/>
+      <c r="G105" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H105" s="67"/>
     </row>
     <row r="106" spans="2:8">
-      <c r="B106" s="62" t="s">
+      <c r="B106" s="61" t="s">
         <v>560</v>
       </c>
-      <c r="C106" s="63"/>
-      <c r="D106" s="64"/>
-      <c r="E106" s="65"/>
-      <c r="F106" s="66"/>
-      <c r="G106" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H106" s="68"/>
+      <c r="C106" s="62"/>
+      <c r="D106" s="63"/>
+      <c r="E106" s="64"/>
+      <c r="F106" s="65"/>
+      <c r="G106" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H106" s="67"/>
     </row>
     <row r="107" spans="2:8">
-      <c r="B107" s="62" t="s">
+      <c r="B107" s="61" t="s">
         <v>561</v>
       </c>
-      <c r="C107" s="63"/>
-      <c r="D107" s="64"/>
-      <c r="E107" s="65"/>
-      <c r="F107" s="66"/>
-      <c r="G107" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H107" s="68"/>
+      <c r="C107" s="62"/>
+      <c r="D107" s="63"/>
+      <c r="E107" s="64"/>
+      <c r="F107" s="65"/>
+      <c r="G107" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H107" s="67"/>
     </row>
     <row r="108" spans="2:8">
-      <c r="B108" s="62" t="s">
+      <c r="B108" s="61" t="s">
         <v>562</v>
       </c>
-      <c r="C108" s="63"/>
-      <c r="D108" s="64"/>
-      <c r="E108" s="65"/>
-      <c r="F108" s="66"/>
-      <c r="G108" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H108" s="68"/>
+      <c r="C108" s="62"/>
+      <c r="D108" s="63"/>
+      <c r="E108" s="64"/>
+      <c r="F108" s="65"/>
+      <c r="G108" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H108" s="67"/>
     </row>
     <row r="109" spans="2:8">
-      <c r="B109" s="62" t="s">
+      <c r="B109" s="61" t="s">
         <v>563</v>
       </c>
-      <c r="C109" s="63"/>
-      <c r="D109" s="64"/>
-      <c r="E109" s="65"/>
-      <c r="F109" s="66"/>
-      <c r="G109" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H109" s="68"/>
+      <c r="C109" s="62"/>
+      <c r="D109" s="63"/>
+      <c r="E109" s="64"/>
+      <c r="F109" s="65"/>
+      <c r="G109" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H109" s="67"/>
     </row>
     <row r="110" spans="2:8">
-      <c r="B110" s="62" t="s">
+      <c r="B110" s="61" t="s">
         <v>564</v>
       </c>
-      <c r="C110" s="63"/>
-      <c r="D110" s="64"/>
-      <c r="E110" s="65"/>
-      <c r="F110" s="66"/>
-      <c r="G110" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H110" s="68"/>
+      <c r="C110" s="62"/>
+      <c r="D110" s="63"/>
+      <c r="E110" s="64"/>
+      <c r="F110" s="65"/>
+      <c r="G110" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H110" s="67"/>
     </row>
     <row r="111" spans="2:8">
-      <c r="B111" s="62" t="s">
+      <c r="B111" s="61" t="s">
         <v>565</v>
       </c>
-      <c r="C111" s="63"/>
-      <c r="D111" s="64"/>
-      <c r="E111" s="65"/>
-      <c r="F111" s="66"/>
-      <c r="G111" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H111" s="68"/>
+      <c r="C111" s="62"/>
+      <c r="D111" s="63"/>
+      <c r="E111" s="64"/>
+      <c r="F111" s="65"/>
+      <c r="G111" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H111" s="67"/>
     </row>
     <row r="112" spans="2:8">
-      <c r="B112" s="62" t="s">
+      <c r="B112" s="61" t="s">
         <v>566</v>
       </c>
-      <c r="C112" s="63"/>
-      <c r="D112" s="64"/>
-      <c r="E112" s="65"/>
-      <c r="F112" s="66"/>
-      <c r="G112" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H112" s="68"/>
+      <c r="C112" s="62"/>
+      <c r="D112" s="63"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="65"/>
+      <c r="G112" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H112" s="67"/>
     </row>
     <row r="113" spans="2:8">
-      <c r="B113" s="62" t="s">
+      <c r="B113" s="61" t="s">
         <v>567</v>
       </c>
-      <c r="C113" s="63"/>
-      <c r="D113" s="64"/>
-      <c r="E113" s="65"/>
-      <c r="F113" s="66"/>
-      <c r="G113" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H113" s="68"/>
+      <c r="C113" s="62"/>
+      <c r="D113" s="63"/>
+      <c r="E113" s="64"/>
+      <c r="F113" s="65"/>
+      <c r="G113" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H113" s="67"/>
     </row>
     <row r="114" spans="2:8">
-      <c r="B114" s="62" t="s">
+      <c r="B114" s="61" t="s">
         <v>568</v>
       </c>
-      <c r="C114" s="63"/>
-      <c r="D114" s="64"/>
-      <c r="E114" s="65"/>
-      <c r="F114" s="66"/>
-      <c r="G114" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H114" s="68"/>
+      <c r="C114" s="62"/>
+      <c r="D114" s="63"/>
+      <c r="E114" s="64"/>
+      <c r="F114" s="65"/>
+      <c r="G114" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H114" s="67"/>
     </row>
     <row r="115" spans="2:8">
-      <c r="B115" s="62" t="s">
+      <c r="B115" s="61" t="s">
         <v>569</v>
       </c>
-      <c r="C115" s="63"/>
-      <c r="D115" s="64"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="66"/>
-      <c r="G115" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H115" s="68"/>
+      <c r="C115" s="62"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="64"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H115" s="67"/>
     </row>
     <row r="116" spans="2:8">
-      <c r="B116" s="62" t="s">
+      <c r="B116" s="61" t="s">
         <v>570</v>
       </c>
-      <c r="C116" s="63"/>
-      <c r="D116" s="64"/>
-      <c r="E116" s="65"/>
-      <c r="F116" s="66"/>
-      <c r="G116" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H116" s="68"/>
+      <c r="C116" s="62"/>
+      <c r="D116" s="63"/>
+      <c r="E116" s="64"/>
+      <c r="F116" s="65"/>
+      <c r="G116" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H116" s="67"/>
     </row>
     <row r="117" spans="2:8">
-      <c r="B117" s="62" t="s">
+      <c r="B117" s="61" t="s">
         <v>571</v>
       </c>
-      <c r="C117" s="63"/>
-      <c r="D117" s="64"/>
-      <c r="E117" s="65"/>
-      <c r="F117" s="66"/>
-      <c r="G117" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H117" s="68"/>
+      <c r="C117" s="62"/>
+      <c r="D117" s="63"/>
+      <c r="E117" s="64"/>
+      <c r="F117" s="65"/>
+      <c r="G117" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H117" s="67"/>
     </row>
     <row r="118" spans="2:8">
-      <c r="B118" s="62" t="s">
+      <c r="B118" s="61" t="s">
         <v>572</v>
       </c>
-      <c r="C118" s="63"/>
-      <c r="D118" s="64"/>
-      <c r="E118" s="65"/>
-      <c r="F118" s="66"/>
-      <c r="G118" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H118" s="68"/>
+      <c r="C118" s="62"/>
+      <c r="D118" s="63"/>
+      <c r="E118" s="64"/>
+      <c r="F118" s="65"/>
+      <c r="G118" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H118" s="67"/>
     </row>
     <row r="119" spans="2:8">
-      <c r="B119" s="62" t="s">
+      <c r="B119" s="61" t="s">
         <v>573</v>
       </c>
-      <c r="C119" s="63"/>
-      <c r="D119" s="64"/>
-      <c r="E119" s="65"/>
-      <c r="F119" s="66"/>
-      <c r="G119" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H119" s="68"/>
+      <c r="C119" s="62"/>
+      <c r="D119" s="63"/>
+      <c r="E119" s="64"/>
+      <c r="F119" s="65"/>
+      <c r="G119" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H119" s="67"/>
     </row>
     <row r="120" spans="2:8">
-      <c r="B120" s="62" t="s">
+      <c r="B120" s="61" t="s">
         <v>574</v>
       </c>
-      <c r="C120" s="63"/>
-      <c r="D120" s="64"/>
-      <c r="E120" s="65"/>
-      <c r="F120" s="66"/>
-      <c r="G120" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H120" s="68"/>
+      <c r="C120" s="62"/>
+      <c r="D120" s="63"/>
+      <c r="E120" s="64"/>
+      <c r="F120" s="65"/>
+      <c r="G120" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H120" s="67"/>
     </row>
     <row r="121" spans="2:8">
-      <c r="B121" s="62" t="s">
+      <c r="B121" s="61" t="s">
         <v>575</v>
       </c>
-      <c r="C121" s="63"/>
-      <c r="D121" s="64"/>
-      <c r="E121" s="65"/>
-      <c r="F121" s="66"/>
-      <c r="G121" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H121" s="68"/>
+      <c r="C121" s="62"/>
+      <c r="D121" s="63"/>
+      <c r="E121" s="64"/>
+      <c r="F121" s="65"/>
+      <c r="G121" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H121" s="67"/>
     </row>
     <row r="122" spans="2:8">
-      <c r="B122" s="62" t="s">
+      <c r="B122" s="61" t="s">
         <v>576</v>
       </c>
-      <c r="C122" s="63"/>
-      <c r="D122" s="64"/>
-      <c r="E122" s="65"/>
-      <c r="F122" s="66"/>
-      <c r="G122" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H122" s="68"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="63"/>
+      <c r="E122" s="64"/>
+      <c r="F122" s="65"/>
+      <c r="G122" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H122" s="67"/>
     </row>
     <row r="123" spans="2:8">
-      <c r="B123" s="62" t="s">
+      <c r="B123" s="61" t="s">
         <v>577</v>
       </c>
-      <c r="C123" s="63"/>
-      <c r="D123" s="64"/>
-      <c r="E123" s="65"/>
-      <c r="F123" s="66"/>
-      <c r="G123" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H123" s="68"/>
+      <c r="C123" s="62"/>
+      <c r="D123" s="63"/>
+      <c r="E123" s="64"/>
+      <c r="F123" s="65"/>
+      <c r="G123" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H123" s="67"/>
     </row>
     <row r="124" spans="2:8">
-      <c r="B124" s="62" t="s">
+      <c r="B124" s="61" t="s">
         <v>578</v>
       </c>
-      <c r="C124" s="63"/>
-      <c r="D124" s="64"/>
-      <c r="E124" s="65"/>
-      <c r="F124" s="66"/>
-      <c r="G124" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H124" s="68"/>
+      <c r="C124" s="62"/>
+      <c r="D124" s="63"/>
+      <c r="E124" s="64"/>
+      <c r="F124" s="65"/>
+      <c r="G124" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H124" s="67"/>
     </row>
     <row r="125" spans="2:8">
-      <c r="B125" s="62" t="s">
+      <c r="B125" s="61" t="s">
         <v>579</v>
       </c>
-      <c r="C125" s="63"/>
-      <c r="D125" s="64"/>
-      <c r="E125" s="65"/>
-      <c r="F125" s="66"/>
-      <c r="G125" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H125" s="68"/>
+      <c r="C125" s="62"/>
+      <c r="D125" s="63"/>
+      <c r="E125" s="64"/>
+      <c r="F125" s="65"/>
+      <c r="G125" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H125" s="67"/>
     </row>
     <row r="126" spans="2:8">
-      <c r="B126" s="62" t="s">
+      <c r="B126" s="61" t="s">
         <v>580</v>
       </c>
-      <c r="C126" s="63"/>
-      <c r="D126" s="64"/>
-      <c r="E126" s="65"/>
-      <c r="F126" s="66"/>
-      <c r="G126" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H126" s="68"/>
+      <c r="C126" s="62"/>
+      <c r="D126" s="63"/>
+      <c r="E126" s="64"/>
+      <c r="F126" s="65"/>
+      <c r="G126" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H126" s="67"/>
     </row>
     <row r="127" spans="2:8">
-      <c r="B127" s="62" t="s">
+      <c r="B127" s="61" t="s">
         <v>581</v>
       </c>
-      <c r="C127" s="63"/>
-      <c r="D127" s="64"/>
-      <c r="E127" s="65"/>
-      <c r="F127" s="66"/>
-      <c r="G127" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H127" s="68"/>
+      <c r="C127" s="62"/>
+      <c r="D127" s="63"/>
+      <c r="E127" s="64"/>
+      <c r="F127" s="65"/>
+      <c r="G127" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H127" s="67"/>
     </row>
     <row r="128" spans="2:8">
-      <c r="B128" s="62" t="s">
+      <c r="B128" s="61" t="s">
         <v>582</v>
       </c>
-      <c r="C128" s="63"/>
-      <c r="D128" s="64"/>
-      <c r="E128" s="65"/>
-      <c r="F128" s="66"/>
-      <c r="G128" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H128" s="68"/>
+      <c r="C128" s="62"/>
+      <c r="D128" s="63"/>
+      <c r="E128" s="64"/>
+      <c r="F128" s="65"/>
+      <c r="G128" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H128" s="67"/>
     </row>
     <row r="129" spans="2:8">
-      <c r="B129" s="62" t="s">
+      <c r="B129" s="61" t="s">
         <v>583</v>
       </c>
-      <c r="C129" s="63"/>
-      <c r="D129" s="64"/>
-      <c r="E129" s="65"/>
-      <c r="F129" s="66"/>
-      <c r="G129" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H129" s="68"/>
+      <c r="C129" s="62"/>
+      <c r="D129" s="63"/>
+      <c r="E129" s="64"/>
+      <c r="F129" s="65"/>
+      <c r="G129" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H129" s="67"/>
     </row>
     <row r="130" spans="2:8">
-      <c r="B130" s="62" t="s">
+      <c r="B130" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="C130" s="63"/>
-      <c r="D130" s="64"/>
-      <c r="E130" s="65"/>
-      <c r="F130" s="66"/>
-      <c r="G130" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H130" s="68"/>
+      <c r="C130" s="62"/>
+      <c r="D130" s="63"/>
+      <c r="E130" s="64"/>
+      <c r="F130" s="65"/>
+      <c r="G130" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H130" s="67"/>
     </row>
     <row r="131" spans="2:8">
-      <c r="B131" s="62" t="s">
+      <c r="B131" s="61" t="s">
         <v>585</v>
       </c>
-      <c r="C131" s="63"/>
-      <c r="D131" s="64"/>
-      <c r="E131" s="65"/>
-      <c r="F131" s="66"/>
-      <c r="G131" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H131" s="68"/>
+      <c r="C131" s="62"/>
+      <c r="D131" s="63"/>
+      <c r="E131" s="64"/>
+      <c r="F131" s="65"/>
+      <c r="G131" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H131" s="67"/>
     </row>
     <row r="132" spans="2:8">
-      <c r="B132" s="62" t="s">
+      <c r="B132" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="C132" s="63"/>
-      <c r="D132" s="64"/>
-      <c r="E132" s="65"/>
-      <c r="F132" s="66"/>
-      <c r="G132" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H132" s="68"/>
+      <c r="C132" s="62"/>
+      <c r="D132" s="63"/>
+      <c r="E132" s="64"/>
+      <c r="F132" s="65"/>
+      <c r="G132" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H132" s="67"/>
     </row>
     <row r="133" spans="2:8">
-      <c r="B133" s="62" t="s">
+      <c r="B133" s="61" t="s">
         <v>587</v>
       </c>
-      <c r="C133" s="63"/>
-      <c r="D133" s="64"/>
-      <c r="E133" s="65"/>
-      <c r="F133" s="66"/>
-      <c r="G133" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H133" s="68"/>
+      <c r="C133" s="62"/>
+      <c r="D133" s="63"/>
+      <c r="E133" s="64"/>
+      <c r="F133" s="65"/>
+      <c r="G133" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H133" s="67"/>
     </row>
     <row r="134" spans="2:8">
-      <c r="B134" s="69" t="str">
+      <c r="B134" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,36,FALSE))</f>
         <v/>
       </c>
-      <c r="C134" s="70"/>
-      <c r="D134" s="71" t="str">
-        <f t="array" ref="D134">SUMPRODUCT(ROUND(D104:D133,2))</f>
-        <v/>
-      </c>
-      <c r="E134" s="71" t="str">
-        <f t="array" ref="E134">SUMPRODUCT(ROUND(E104:E133,2))</f>
-        <v/>
-      </c>
-      <c r="F134" s="71" t="str">
-        <f t="array" ref="F134">SUMPRODUCT(ROUND(F104:F133,2))</f>
-        <v/>
-      </c>
-      <c r="G134" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H134" s="73"/>
+      <c r="C134" s="69"/>
+      <c r="D134" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(D104:D133,2))</f>
+        <v/>
+      </c>
+      <c r="E134" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(E104:E133,2))</f>
+        <v/>
+      </c>
+      <c r="F134" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(F104:F133,2))</f>
+        <v/>
+      </c>
+      <c r="G134" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H134" s="72"/>
     </row>
     <row r="135" spans="2:8">
-      <c r="B135" s="57" t="s">
+      <c r="B135" s="56" t="s">
         <v>588</v>
       </c>
-      <c r="C135" s="58" t="str">
+      <c r="C135" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,37,FALSE))</f>
         <v/>
       </c>
-      <c r="D135" s="59"/>
-      <c r="E135" s="59"/>
-      <c r="F135" s="59"/>
-      <c r="G135" s="60"/>
-      <c r="H135" s="61"/>
+      <c r="D135" s="58"/>
+      <c r="E135" s="58"/>
+      <c r="F135" s="58"/>
+      <c r="G135" s="59"/>
+      <c r="H135" s="60"/>
     </row>
     <row r="136" spans="2:8">
-      <c r="B136" s="62" t="s">
+      <c r="B136" s="61" t="s">
         <v>589</v>
       </c>
-      <c r="C136" s="63"/>
-      <c r="D136" s="64"/>
-      <c r="E136" s="65"/>
-      <c r="F136" s="66"/>
-      <c r="G136" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H136" s="68"/>
+      <c r="C136" s="62"/>
+      <c r="D136" s="63"/>
+      <c r="E136" s="64"/>
+      <c r="F136" s="65"/>
+      <c r="G136" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H136" s="67"/>
     </row>
     <row r="137" spans="2:8">
-      <c r="B137" s="62" t="s">
+      <c r="B137" s="61" t="s">
         <v>590</v>
       </c>
-      <c r="C137" s="63"/>
-      <c r="D137" s="64"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="66"/>
-      <c r="G137" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H137" s="68"/>
+      <c r="C137" s="62"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="64"/>
+      <c r="F137" s="65"/>
+      <c r="G137" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H137" s="67"/>
     </row>
     <row r="138" spans="2:8">
-      <c r="B138" s="62" t="s">
+      <c r="B138" s="61" t="s">
         <v>591</v>
       </c>
-      <c r="C138" s="63"/>
-      <c r="D138" s="64"/>
-      <c r="E138" s="65"/>
-      <c r="F138" s="66"/>
-      <c r="G138" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H138" s="68"/>
+      <c r="C138" s="62"/>
+      <c r="D138" s="63"/>
+      <c r="E138" s="64"/>
+      <c r="F138" s="65"/>
+      <c r="G138" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H138" s="67"/>
     </row>
     <row r="139" spans="2:8">
-      <c r="B139" s="62" t="s">
+      <c r="B139" s="61" t="s">
         <v>592</v>
       </c>
-      <c r="C139" s="63"/>
-      <c r="D139" s="64"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="66"/>
-      <c r="G139" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H139" s="68"/>
+      <c r="C139" s="62"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="64"/>
+      <c r="F139" s="65"/>
+      <c r="G139" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H139" s="67"/>
     </row>
     <row r="140" spans="2:8">
-      <c r="B140" s="62" t="s">
+      <c r="B140" s="61" t="s">
         <v>593</v>
       </c>
-      <c r="C140" s="63"/>
-      <c r="D140" s="64"/>
-      <c r="E140" s="65"/>
-      <c r="F140" s="66"/>
-      <c r="G140" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H140" s="68"/>
+      <c r="C140" s="62"/>
+      <c r="D140" s="63"/>
+      <c r="E140" s="64"/>
+      <c r="F140" s="65"/>
+      <c r="G140" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H140" s="67"/>
     </row>
     <row r="141" spans="2:8">
-      <c r="B141" s="62" t="s">
+      <c r="B141" s="61" t="s">
         <v>594</v>
       </c>
-      <c r="C141" s="63"/>
-      <c r="D141" s="64"/>
-      <c r="E141" s="65"/>
-      <c r="F141" s="66"/>
-      <c r="G141" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H141" s="68"/>
+      <c r="C141" s="62"/>
+      <c r="D141" s="63"/>
+      <c r="E141" s="64"/>
+      <c r="F141" s="65"/>
+      <c r="G141" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H141" s="67"/>
     </row>
     <row r="142" spans="2:8">
-      <c r="B142" s="62" t="s">
+      <c r="B142" s="61" t="s">
         <v>595</v>
       </c>
-      <c r="C142" s="63"/>
-      <c r="D142" s="64"/>
-      <c r="E142" s="65"/>
-      <c r="F142" s="66"/>
-      <c r="G142" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H142" s="68"/>
+      <c r="C142" s="62"/>
+      <c r="D142" s="63"/>
+      <c r="E142" s="64"/>
+      <c r="F142" s="65"/>
+      <c r="G142" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H142" s="67"/>
     </row>
     <row r="143" spans="2:8">
-      <c r="B143" s="62" t="s">
+      <c r="B143" s="61" t="s">
         <v>596</v>
       </c>
-      <c r="C143" s="63"/>
-      <c r="D143" s="64"/>
-      <c r="E143" s="65"/>
-      <c r="F143" s="66"/>
-      <c r="G143" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H143" s="68"/>
+      <c r="C143" s="62"/>
+      <c r="D143" s="63"/>
+      <c r="E143" s="64"/>
+      <c r="F143" s="65"/>
+      <c r="G143" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H143" s="67"/>
     </row>
     <row r="144" spans="2:8">
-      <c r="B144" s="62" t="s">
+      <c r="B144" s="61" t="s">
         <v>597</v>
       </c>
-      <c r="C144" s="63"/>
-      <c r="D144" s="64"/>
-      <c r="E144" s="65"/>
-      <c r="F144" s="66"/>
-      <c r="G144" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H144" s="68"/>
+      <c r="C144" s="62"/>
+      <c r="D144" s="63"/>
+      <c r="E144" s="64"/>
+      <c r="F144" s="65"/>
+      <c r="G144" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H144" s="67"/>
     </row>
     <row r="145" spans="2:8">
-      <c r="B145" s="62" t="s">
+      <c r="B145" s="61" t="s">
         <v>598</v>
       </c>
-      <c r="C145" s="63"/>
-      <c r="D145" s="64"/>
-      <c r="E145" s="65"/>
-      <c r="F145" s="66"/>
-      <c r="G145" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H145" s="68"/>
+      <c r="C145" s="62"/>
+      <c r="D145" s="63"/>
+      <c r="E145" s="64"/>
+      <c r="F145" s="65"/>
+      <c r="G145" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H145" s="67"/>
     </row>
     <row r="146" spans="2:8">
-      <c r="B146" s="62" t="s">
+      <c r="B146" s="61" t="s">
         <v>599</v>
       </c>
-      <c r="C146" s="63"/>
-      <c r="D146" s="64"/>
-      <c r="E146" s="65"/>
-      <c r="F146" s="66"/>
-      <c r="G146" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H146" s="68"/>
+      <c r="C146" s="62"/>
+      <c r="D146" s="63"/>
+      <c r="E146" s="64"/>
+      <c r="F146" s="65"/>
+      <c r="G146" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H146" s="67"/>
     </row>
     <row r="147" spans="2:8">
-      <c r="B147" s="62" t="s">
+      <c r="B147" s="61" t="s">
         <v>600</v>
       </c>
-      <c r="C147" s="63"/>
-      <c r="D147" s="64"/>
-      <c r="E147" s="65"/>
-      <c r="F147" s="66"/>
-      <c r="G147" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H147" s="68"/>
+      <c r="C147" s="62"/>
+      <c r="D147" s="63"/>
+      <c r="E147" s="64"/>
+      <c r="F147" s="65"/>
+      <c r="G147" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H147" s="67"/>
     </row>
     <row r="148" spans="2:8">
-      <c r="B148" s="62" t="s">
+      <c r="B148" s="61" t="s">
         <v>601</v>
       </c>
-      <c r="C148" s="63"/>
-      <c r="D148" s="64"/>
-      <c r="E148" s="65"/>
-      <c r="F148" s="66"/>
-      <c r="G148" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H148" s="68"/>
+      <c r="C148" s="62"/>
+      <c r="D148" s="63"/>
+      <c r="E148" s="64"/>
+      <c r="F148" s="65"/>
+      <c r="G148" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H148" s="67"/>
     </row>
     <row r="149" spans="2:8">
-      <c r="B149" s="62" t="s">
+      <c r="B149" s="61" t="s">
         <v>602</v>
       </c>
-      <c r="C149" s="63"/>
-      <c r="D149" s="64"/>
-      <c r="E149" s="65"/>
-      <c r="F149" s="66"/>
-      <c r="G149" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H149" s="68"/>
+      <c r="C149" s="62"/>
+      <c r="D149" s="63"/>
+      <c r="E149" s="64"/>
+      <c r="F149" s="65"/>
+      <c r="G149" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H149" s="67"/>
     </row>
     <row r="150" spans="2:8">
-      <c r="B150" s="62" t="s">
+      <c r="B150" s="61" t="s">
         <v>603</v>
       </c>
-      <c r="C150" s="63"/>
-      <c r="D150" s="64"/>
-      <c r="E150" s="65"/>
-      <c r="F150" s="66"/>
-      <c r="G150" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H150" s="68"/>
+      <c r="C150" s="62"/>
+      <c r="D150" s="63"/>
+      <c r="E150" s="64"/>
+      <c r="F150" s="65"/>
+      <c r="G150" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H150" s="67"/>
     </row>
     <row r="151" spans="2:8">
-      <c r="B151" s="62" t="s">
+      <c r="B151" s="61" t="s">
         <v>604</v>
       </c>
-      <c r="C151" s="63"/>
-      <c r="D151" s="64"/>
-      <c r="E151" s="65"/>
-      <c r="F151" s="66"/>
-      <c r="G151" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H151" s="68"/>
+      <c r="C151" s="62"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="64"/>
+      <c r="F151" s="65"/>
+      <c r="G151" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H151" s="67"/>
     </row>
     <row r="152" spans="2:8">
-      <c r="B152" s="62" t="s">
+      <c r="B152" s="61" t="s">
         <v>605</v>
       </c>
-      <c r="C152" s="63"/>
-      <c r="D152" s="64"/>
-      <c r="E152" s="65"/>
-      <c r="F152" s="66"/>
-      <c r="G152" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H152" s="68"/>
+      <c r="C152" s="62"/>
+      <c r="D152" s="63"/>
+      <c r="E152" s="64"/>
+      <c r="F152" s="65"/>
+      <c r="G152" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H152" s="67"/>
     </row>
     <row r="153" spans="2:8">
-      <c r="B153" s="62" t="s">
+      <c r="B153" s="61" t="s">
         <v>606</v>
       </c>
-      <c r="C153" s="63"/>
-      <c r="D153" s="64"/>
-      <c r="E153" s="65"/>
-      <c r="F153" s="66"/>
-      <c r="G153" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H153" s="68"/>
+      <c r="C153" s="62"/>
+      <c r="D153" s="63"/>
+      <c r="E153" s="64"/>
+      <c r="F153" s="65"/>
+      <c r="G153" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H153" s="67"/>
     </row>
     <row r="154" spans="2:8">
-      <c r="B154" s="62" t="s">
+      <c r="B154" s="61" t="s">
         <v>607</v>
       </c>
-      <c r="C154" s="63"/>
-      <c r="D154" s="64"/>
-      <c r="E154" s="65"/>
-      <c r="F154" s="66"/>
-      <c r="G154" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H154" s="68"/>
+      <c r="C154" s="62"/>
+      <c r="D154" s="63"/>
+      <c r="E154" s="64"/>
+      <c r="F154" s="65"/>
+      <c r="G154" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H154" s="67"/>
     </row>
     <row r="155" spans="2:8">
-      <c r="B155" s="62" t="s">
+      <c r="B155" s="61" t="s">
         <v>608</v>
       </c>
-      <c r="C155" s="63"/>
-      <c r="D155" s="64"/>
-      <c r="E155" s="65"/>
-      <c r="F155" s="66"/>
-      <c r="G155" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H155" s="68"/>
+      <c r="C155" s="62"/>
+      <c r="D155" s="63"/>
+      <c r="E155" s="64"/>
+      <c r="F155" s="65"/>
+      <c r="G155" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H155" s="67"/>
     </row>
     <row r="156" spans="2:8">
-      <c r="B156" s="69" t="str">
+      <c r="B156" s="68" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,38,FALSE))</f>
         <v/>
       </c>
-      <c r="C156" s="70"/>
-      <c r="D156" s="71" t="str">
-        <f t="array" ref="D156">SUMPRODUCT(ROUND(D136:D155,2))</f>
-        <v/>
-      </c>
-      <c r="E156" s="71" t="str">
-        <f t="array" ref="E156">SUMPRODUCT(ROUND(E136:E155,2))</f>
-        <v/>
-      </c>
-      <c r="F156" s="71" t="str">
-        <f t="array" ref="F156">SUMPRODUCT(ROUND(F136:F155,2))</f>
-        <v/>
-      </c>
-      <c r="G156" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H156" s="73"/>
+      <c r="C156" s="69"/>
+      <c r="D156" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(D136:D155,2))</f>
+        <v/>
+      </c>
+      <c r="E156" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(E136:E155,2))</f>
+        <v/>
+      </c>
+      <c r="F156" s="70" t="str">
+        <f>SUMPRODUCT(ROUND(F136:F155,2))</f>
+        <v/>
+      </c>
+      <c r="G156" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H156" s="72"/>
     </row>
     <row r="157" spans="2:8">
-      <c r="B157" s="57" t="s">
+      <c r="B157" s="56" t="s">
         <v>609</v>
       </c>
-      <c r="C157" s="74" t="str">
+      <c r="C157" s="73" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,39,FALSE))</f>
         <v/>
       </c>
-      <c r="D157" s="64"/>
-      <c r="E157" s="65"/>
-      <c r="F157" s="66"/>
-      <c r="G157" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H157" s="68"/>
+      <c r="D157" s="63"/>
+      <c r="E157" s="64"/>
+      <c r="F157" s="65"/>
+      <c r="G157" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H157" s="67"/>
     </row>
     <row r="158" spans="2:8">
-      <c r="B158" s="57" t="s">
+      <c r="B158" s="56" t="s">
         <v>610</v>
       </c>
-      <c r="C158" s="74" t="str">
+      <c r="C158" s="73" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,40,FALSE))</f>
         <v/>
       </c>
-      <c r="D158" s="64"/>
-      <c r="E158" s="65"/>
-      <c r="F158" s="66"/>
-      <c r="G158" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H158" s="68"/>
+      <c r="D158" s="63"/>
+      <c r="E158" s="64"/>
+      <c r="F158" s="65"/>
+      <c r="G158" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H158" s="67"/>
     </row>
     <row r="159" spans="2:8">
-      <c r="B159" s="57" t="s">
+      <c r="B159" s="56" t="s">
         <v>611</v>
       </c>
-      <c r="C159" s="75" t="str">
+      <c r="C159" s="74" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,41,FALSE))</f>
         <v/>
       </c>
-      <c r="D159" s="64"/>
-      <c r="E159" s="65"/>
-      <c r="F159" s="66"/>
-      <c r="G159" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H159" s="68"/>
+      <c r="D159" s="63"/>
+      <c r="E159" s="64"/>
+      <c r="F159" s="65"/>
+      <c r="G159" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H159" s="67"/>
     </row>
     <row r="160" spans="2:8">
-      <c r="B160" s="76" t="str">
+      <c r="B160" s="75" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,42,FALSE))</f>
         <v/>
       </c>
-      <c r="C160" s="77"/>
-      <c r="D160" s="78" t="str">
+      <c r="C160" s="76"/>
+      <c r="D160" s="77" t="str">
         <f>SUM(D48+D70+D102+D134+D156+D157+D158+D159)</f>
         <v/>
       </c>
-      <c r="E160" s="78" t="str">
+      <c r="E160" s="77" t="str">
         <f>SUM(E48+E70+E102+E134+E156+E157+E158+E159)</f>
         <v/>
       </c>
-      <c r="F160" s="78" t="str">
+      <c r="F160" s="77" t="str">
         <f>SUM(F48+F70+F102+F134+F156+F157+F158+F159)</f>
         <v/>
       </c>
-      <c r="G160" s="67" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H160" s="80"/>
+      <c r="G160" s="66" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H160" s="79"/>
     </row>
     <row r="164" spans="2:5">
-      <c r="E164" s="82" t="str">
+      <c r="E164" s="81" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,44,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="165" spans="2:5">
-      <c r="B165" s="81" t="str">
+      <c r="B165" s="80" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,43,FALSE))</f>
         <v/>
       </c>
-      <c r="C165" s="81"/>
-      <c r="D165" s="81"/>
-      <c r="E165" s="82"/>
+      <c r="C165" s="80"/>
+      <c r="D165" s="80"/>
+      <c r="E165" s="81"/>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
-      <c r="D166" s="83"/>
-      <c r="E166" s="83" t="str">
+      <c r="D166" s="82"/>
+      <c r="E166" s="82" t="str">
         <f>B13</f>
         <v/>
       </c>
     </row>
     <row r="168" spans="2:5">
-      <c r="B168" s="84" t="str">
+      <c r="B168" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,45,FALSE))</f>
         <v/>
       </c>
-      <c r="C168" s="6"/>
-      <c r="D168" s="85" t="str">
+      <c r="C168" s="57"/>
+      <c r="D168" s="83" t="str">
         <f>IF(ROUND(E168;2)=ROUND(F20-F160;2);"✓";"")</f>
         <v/>
       </c>
-      <c r="E168" s="86" t="str">
+      <c r="E168" s="65" t="str">
         <f>E20-E160</f>
         <v/>
       </c>
     </row>
     <row r="170" spans="2:5">
-      <c r="B170" s="84" t="str">
+      <c r="B170" s="57" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,46,FALSE))</f>
         <v/>
       </c>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="87" t="str">
+      <c r="C170" s="57"/>
+      <c r="D170" s="57"/>
+      <c r="E170" s="84" t="str">
         <f>IF(E168=SUM(E170:E172);"OK";"")</f>
         <v/>
       </c>
     </row>
     <row r="171" spans="2:5">
-      <c r="B171" s="6" t="str">
+      <c r="B171" s="85" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,47,FALSE))</f>
         <v/>
       </c>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="86"/>
+      <c r="C171" s="85"/>
+      <c r="D171" s="85"/>
+      <c r="E171" s="65"/>
     </row>
     <row r="172" spans="2:5">
-      <c r="B172" s="6" t="str">
+      <c r="B172" s="85" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,48,FALSE))</f>
         <v/>
       </c>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="86"/>
+      <c r="C172" s="85"/>
+      <c r="D172" s="85"/>
+      <c r="E172" s="65"/>
     </row>
     <row r="173" spans="2:5">
-      <c r="B173" s="6" t="str">
+      <c r="B173" s="85" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,49,FALSE))</f>
         <v/>
       </c>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="86"/>
+      <c r="C173" s="85"/>
+      <c r="D173" s="85"/>
+      <c r="E173" s="65"/>
     </row>
     <row r="174" spans="2:5">
       <c r="B174" s="6"/>
@@ -7577,12 +7586,12 @@
       <c r="E182" s="6"/>
     </row>
     <row r="183" spans="2:5">
-      <c r="B183" s="84" t="str">
+      <c r="B183" s="86" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,51,FALSE))</f>
         <v/>
       </c>
       <c r="C183" s="6"/>
-      <c r="D183" s="84" t="str">
+      <c r="D183" s="86" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,52,FALSE))</f>
         <v/>
       </c>

--- a/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
+++ b/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
@@ -2327,7 +2327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2503,16 +2503,13 @@
     <xf numFmtId="165" fontId="5" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2522,9 +2519,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5824,7 +5818,7 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v/>
       </c>
-      <c r="H48" s="72"/>
+      <c r="H48" s="71"/>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="56" t="s">
@@ -6142,7 +6136,7 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v/>
       </c>
-      <c r="H70" s="72"/>
+      <c r="H70" s="71"/>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" s="56" t="s">
@@ -6600,7 +6594,7 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v/>
       </c>
-      <c r="H102" s="72"/>
+      <c r="H102" s="71"/>
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="56" t="s">
@@ -7058,7 +7052,7 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v/>
       </c>
-      <c r="H134" s="72"/>
+      <c r="H134" s="71"/>
     </row>
     <row r="135" spans="2:8">
       <c r="B135" s="56" t="s">
@@ -7376,13 +7370,13 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v/>
       </c>
-      <c r="H156" s="72"/>
+      <c r="H156" s="71"/>
     </row>
     <row r="157" spans="2:8">
       <c r="B157" s="56" t="s">
         <v>609</v>
       </c>
-      <c r="C157" s="73" t="str">
+      <c r="C157" s="72" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,39,FALSE))</f>
         <v/>
       </c>
@@ -7399,7 +7393,7 @@
       <c r="B158" s="56" t="s">
         <v>610</v>
       </c>
-      <c r="C158" s="73" t="str">
+      <c r="C158" s="72" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,40,FALSE))</f>
         <v/>
       </c>
@@ -7416,7 +7410,7 @@
       <c r="B159" s="56" t="s">
         <v>611</v>
       </c>
-      <c r="C159" s="74" t="str">
+      <c r="C159" s="73" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,41,FALSE))</f>
         <v/>
       </c>
@@ -7430,20 +7424,20 @@
       <c r="H159" s="67"/>
     </row>
     <row r="160" spans="2:8">
-      <c r="B160" s="75" t="str">
+      <c r="B160" s="74" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,42,FALSE))</f>
         <v/>
       </c>
-      <c r="C160" s="76"/>
-      <c r="D160" s="77" t="str">
+      <c r="C160" s="75"/>
+      <c r="D160" s="76" t="str">
         <f>SUM(D48+D70+D102+D134+D156+D157+D158+D159)</f>
         <v/>
       </c>
-      <c r="E160" s="77" t="str">
+      <c r="E160" s="76" t="str">
         <f>SUM(E48+E70+E102+E134+E156+E157+E158+E159)</f>
         <v/>
       </c>
-      <c r="F160" s="77" t="str">
+      <c r="F160" s="76" t="str">
         <f>SUM(F48+F70+F102+F134+F156+F157+F158+F159)</f>
         <v/>
       </c>
@@ -7451,28 +7445,28 @@
         <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
         <v/>
       </c>
-      <c r="H160" s="79"/>
+      <c r="H160" s="77"/>
     </row>
     <row r="164" spans="2:5">
-      <c r="E164" s="81" t="str">
+      <c r="E164" s="79" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,44,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="165" spans="2:5">
-      <c r="B165" s="80" t="str">
+      <c r="B165" s="78" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,43,FALSE))</f>
         <v/>
       </c>
-      <c r="C165" s="80"/>
-      <c r="D165" s="80"/>
-      <c r="E165" s="81"/>
+      <c r="C165" s="78"/>
+      <c r="D165" s="78"/>
+      <c r="E165" s="79"/>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
-      <c r="D166" s="82"/>
-      <c r="E166" s="82" t="str">
+      <c r="D166" s="80"/>
+      <c r="E166" s="80" t="str">
         <f>B13</f>
         <v/>
       </c>
@@ -7483,7 +7477,7 @@
         <v/>
       </c>
       <c r="C168" s="57"/>
-      <c r="D168" s="83" t="str">
+      <c r="D168" s="81" t="str">
         <f>IF(ROUND(E168;2)=ROUND(F20-F160;2);"✓";"")</f>
         <v/>
       </c>
@@ -7499,36 +7493,36 @@
       </c>
       <c r="C170" s="57"/>
       <c r="D170" s="57"/>
-      <c r="E170" s="84" t="str">
+      <c r="E170" s="82" t="str">
         <f>IF(E168=SUM(E170:E172);"OK";"")</f>
         <v/>
       </c>
     </row>
     <row r="171" spans="2:5">
-      <c r="B171" s="85" t="str">
+      <c r="B171" s="83" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,47,FALSE))</f>
         <v/>
       </c>
-      <c r="C171" s="85"/>
-      <c r="D171" s="85"/>
+      <c r="C171" s="83"/>
+      <c r="D171" s="83"/>
       <c r="E171" s="65"/>
     </row>
     <row r="172" spans="2:5">
-      <c r="B172" s="85" t="str">
+      <c r="B172" s="83" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,48,FALSE))</f>
         <v/>
       </c>
-      <c r="C172" s="85"/>
-      <c r="D172" s="85"/>
+      <c r="C172" s="83"/>
+      <c r="D172" s="83"/>
       <c r="E172" s="65"/>
     </row>
     <row r="173" spans="2:5">
-      <c r="B173" s="85" t="str">
+      <c r="B173" s="83" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,49,FALSE))</f>
         <v/>
       </c>
-      <c r="C173" s="85"/>
-      <c r="D173" s="85"/>
+      <c r="C173" s="83"/>
+      <c r="D173" s="83"/>
       <c r="E173" s="65"/>
     </row>
     <row r="174" spans="2:5">
@@ -7586,12 +7580,12 @@
       <c r="E182" s="6"/>
     </row>
     <row r="183" spans="2:5">
-      <c r="B183" s="86" t="str">
+      <c r="B183" s="84" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,51,FALSE))</f>
         <v/>
       </c>
       <c r="C183" s="6"/>
-      <c r="D183" s="86" t="str">
+      <c r="D183" s="84" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,52,FALSE))</f>
         <v/>
       </c>

--- a/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
+++ b/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
@@ -1864,7 +1864,7 @@
     <numFmt numFmtId="167" formatCode="0%"/>
     <numFmt numFmtId="168" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1904,6 +1904,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2327,7 +2335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2494,36 +2502,30 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2536,7 +2538,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5814,11 +5816,11 @@
         <f>SUMPRODUCT(ROUND(F28:F47,2))</f>
         <v/>
       </c>
-      <c r="G48" s="66" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H48" s="71"/>
+      <c r="G48" s="71" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="72"/>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="56" t="s">
@@ -6132,11 +6134,11 @@
         <f>SUMPRODUCT(ROUND(F50:F69,2))</f>
         <v/>
       </c>
-      <c r="G70" s="66" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H70" s="71"/>
+      <c r="G70" s="71" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H70" s="72"/>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" s="56" t="s">
@@ -6590,11 +6592,11 @@
         <f>SUMPRODUCT(ROUND(F72:F101,2))</f>
         <v/>
       </c>
-      <c r="G102" s="66" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H102" s="71"/>
+      <c r="G102" s="71" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H102" s="72"/>
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="56" t="s">
@@ -7048,11 +7050,11 @@
         <f>SUMPRODUCT(ROUND(F104:F133,2))</f>
         <v/>
       </c>
-      <c r="G134" s="66" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H134" s="71"/>
+      <c r="G134" s="71" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H134" s="72"/>
     </row>
     <row r="135" spans="2:8">
       <c r="B135" s="56" t="s">
@@ -7366,17 +7368,17 @@
         <f>SUMPRODUCT(ROUND(F136:F155,2))</f>
         <v/>
       </c>
-      <c r="G156" s="66" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H156" s="71"/>
+      <c r="G156" s="71" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H156" s="72"/>
     </row>
     <row r="157" spans="2:8">
       <c r="B157" s="56" t="s">
         <v>609</v>
       </c>
-      <c r="C157" s="72" t="str">
+      <c r="C157" s="73" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,39,FALSE))</f>
         <v/>
       </c>
@@ -7393,7 +7395,7 @@
       <c r="B158" s="56" t="s">
         <v>610</v>
       </c>
-      <c r="C158" s="72" t="str">
+      <c r="C158" s="73" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,40,FALSE))</f>
         <v/>
       </c>
@@ -7410,7 +7412,7 @@
       <c r="B159" s="56" t="s">
         <v>611</v>
       </c>
-      <c r="C159" s="73" t="str">
+      <c r="C159" s="74" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,41,FALSE))</f>
         <v/>
       </c>
@@ -7424,49 +7426,49 @@
       <c r="H159" s="67"/>
     </row>
     <row r="160" spans="2:8">
-      <c r="B160" s="74" t="str">
+      <c r="B160" s="75" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,42,FALSE))</f>
         <v/>
       </c>
-      <c r="C160" s="75"/>
-      <c r="D160" s="76" t="str">
+      <c r="C160" s="76"/>
+      <c r="D160" s="77" t="str">
         <f>SUM(D48+D70+D102+D134+D156+D157+D158+D159)</f>
         <v/>
       </c>
-      <c r="E160" s="76" t="str">
+      <c r="E160" s="77" t="str">
         <f>SUM(E48+E70+E102+E134+E156+E157+E158+E159)</f>
         <v/>
       </c>
-      <c r="F160" s="76" t="str">
+      <c r="F160" s="77" t="str">
         <f>SUM(F48+F70+F102+F134+F156+F157+F158+F159)</f>
         <v/>
       </c>
-      <c r="G160" s="66" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H160" s="77"/>
+      <c r="G160" s="78" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H160" s="79"/>
     </row>
     <row r="164" spans="2:5">
-      <c r="E164" s="79" t="str">
+      <c r="E164" s="81" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,44,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="165" spans="2:5">
-      <c r="B165" s="78" t="str">
+      <c r="B165" s="80" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,43,FALSE))</f>
         <v/>
       </c>
-      <c r="C165" s="78"/>
-      <c r="D165" s="78"/>
-      <c r="E165" s="79"/>
+      <c r="C165" s="80"/>
+      <c r="D165" s="80"/>
+      <c r="E165" s="81"/>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
-      <c r="D166" s="80"/>
-      <c r="E166" s="80" t="str">
+      <c r="D166" s="82"/>
+      <c r="E166" s="82" t="str">
         <f>B13</f>
         <v/>
       </c>
@@ -7477,7 +7479,7 @@
         <v/>
       </c>
       <c r="C168" s="57"/>
-      <c r="D168" s="81" t="str">
+      <c r="D168" s="83" t="str">
         <f>IF(ROUND(E168;2)=ROUND(F20-F160;2);"✓";"")</f>
         <v/>
       </c>
@@ -7493,36 +7495,36 @@
       </c>
       <c r="C170" s="57"/>
       <c r="D170" s="57"/>
-      <c r="E170" s="82" t="str">
+      <c r="E170" s="84" t="str">
         <f>IF(E168=SUM(E170:E172);"OK";"")</f>
         <v/>
       </c>
     </row>
     <row r="171" spans="2:5">
-      <c r="B171" s="83" t="str">
+      <c r="B171" s="85" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,47,FALSE))</f>
         <v/>
       </c>
-      <c r="C171" s="83"/>
-      <c r="D171" s="83"/>
+      <c r="C171" s="85"/>
+      <c r="D171" s="85"/>
       <c r="E171" s="65"/>
     </row>
     <row r="172" spans="2:5">
-      <c r="B172" s="83" t="str">
+      <c r="B172" s="85" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,48,FALSE))</f>
         <v/>
       </c>
-      <c r="C172" s="83"/>
-      <c r="D172" s="83"/>
+      <c r="C172" s="85"/>
+      <c r="D172" s="85"/>
       <c r="E172" s="65"/>
     </row>
     <row r="173" spans="2:5">
-      <c r="B173" s="83" t="str">
+      <c r="B173" s="85" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,49,FALSE))</f>
         <v/>
       </c>
-      <c r="C173" s="83"/>
-      <c r="D173" s="83"/>
+      <c r="C173" s="85"/>
+      <c r="D173" s="85"/>
       <c r="E173" s="65"/>
     </row>
     <row r="174" spans="2:5">
@@ -7580,12 +7582,12 @@
       <c r="E182" s="6"/>
     </row>
     <row r="183" spans="2:5">
-      <c r="B183" s="84" t="str">
+      <c r="B183" s="86" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,51,FALSE))</f>
         <v/>
       </c>
       <c r="C183" s="6"/>
-      <c r="D183" s="84" t="str">
+      <c r="D183" s="86" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,52,FALSE))</f>
         <v/>
       </c>

--- a/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
+++ b/Test-Dateien/D_Finanzbericht_TEST_DE_Unprotected.xlsx
@@ -1860,11 +1860,11 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="mm-dd-yy"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1874,29 +1874,25 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0563C1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1906,12 +1902,10 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1965,7 +1959,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2025,17 +2019,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -2073,18 +2056,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="medium">
         <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -2104,9 +2078,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2117,39 +2089,6 @@
         <color auto="1"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -2167,12 +2106,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2181,16 +2124,24 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2206,19 +2157,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2243,18 +2181,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -2291,14 +2220,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      </right>
+      <top style="medium">
         <color auto="1"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2308,24 +2237,18 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -2335,215 +2258,191 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2840,7 +2739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V184"/>
+  <dimension ref="B1:V184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2913,7 +2812,10 @@
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="7">
+        <f>IF($E$2="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
+        <v>0</v>
+      </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
@@ -2922,17 +2824,15 @@
       <c r="O3" s="8"/>
     </row>
     <row r="4" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <f>HYPERLINK(VLOOKUP($E$2,Sprachversionen!$B:$BN,62,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
     </row>
     <row r="5" spans="2:22" ht="12" customHeight="1">
       <c r="B5" s="6">
@@ -2940,8 +2840,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="11"/>
-      <c r="J5" s="12"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="6">
@@ -2949,20 +2848,20 @@
         <v>0</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="2:22">
@@ -2971,19 +2870,19 @@
         <v>0</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="15">
+      <c r="D8" s="12">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,7,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="15">
+      <c r="E8" s="13"/>
+      <c r="F8" s="12">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,8,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="18">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="J8" s="15"/>
+      <c r="K8">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,59,FALSE))</f>
         <v>0</v>
       </c>
@@ -2994,2903 +2893,2890 @@
         <v>0</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="15">
+      <c r="D9" s="12">
         <f>D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="15">
+      <c r="E9" s="13">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
         <f>F8</f>
         <v>0</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="J9" s="19"/>
-    </row>
-    <row r="11" spans="2:22" ht="13.5" customHeight="1">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22">
+      <c r="G9" s="13">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="2:22" ht="13.5" customHeight="1"/>
+    <row r="11" spans="2:22" ht="12.75" customHeight="1">
+      <c r="B11" s="17">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="23">
+      <c r="D11" s="19">
+        <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,11,FALSE))</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,12,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="19">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,13,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="19">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,14,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="21">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,15,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="18">
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="K11" s="25"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="27"/>
-      <c r="Q11" s="25">
+      <c r="K11" s="18"/>
+      <c r="Q11" s="18">
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="R11" s="25"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="27"/>
-    </row>
-    <row r="12" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B12" s="28">
+      <c r="R11" s="18"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="22">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,9,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="24"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="30"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="30"/>
-    </row>
-    <row r="13" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B13" s="31">
+      <c r="C12" s="22"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="21"/>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="B13" s="23">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,10,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="24"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="32">
+      <c r="C13" s="23"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="21"/>
+      <c r="L13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="M13" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="24">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="32">
+      <c r="S13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,22,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="T13" s="32" t="s">
+      <c r="T13" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="32">
+      <c r="U13" s="24">
         <f>IF(E3="",VLOOKUP($E$2,Sprachversionen!$B:$BN,28,FALSE),E3)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="33">
+      <c r="V13" s="24">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,58,FALSE))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="24"/>
-      <c r="J14" s="36" t="s">
+    <row r="14" spans="2:22">
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="21"/>
+      <c r="J14" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L14" s="38"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="36" t="s">
+      <c r="L14" s="43"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="45">
+        <f>IF(M14="","",N14/M14)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="37">
+      <c r="R14" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S14" s="38"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S14" s="43"/>
+      <c r="T14" s="44"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="45">
+        <f>IF(T14="","",U14/T14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="41">
+      <c r="B15" s="27">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,16,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
-      <c r="J15" s="36" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="28">
+        <v>0</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="32"/>
+      <c r="J15" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L15" s="38"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="36" t="s">
+      <c r="L15" s="43"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="45">
+        <f>IF(M15="","",N15/M15)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="R15" s="37">
+      <c r="R15" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S15" s="38"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B16" s="46">
+      <c r="S15" s="43"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="45">
+        <f>IF(T15="","",U15/T15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="B16" s="27">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,17,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="42">
-        <v>0</v>
-      </c>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="47">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="45"/>
-      <c r="J16" s="36" t="s">
+      <c r="C16" s="27"/>
+      <c r="D16" s="28">
+        <v>0</v>
+      </c>
+      <c r="E16" s="29"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31">
+        <f>IFERROR(F16/D16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="32"/>
+      <c r="J16" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L16" s="38"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36" t="s">
+      <c r="L16" s="43"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="45">
+        <f>IF(M16="","",N16/M16)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="37">
+      <c r="R16" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S16" s="38"/>
-      <c r="T16" s="39"/>
-      <c r="U16" s="39"/>
-      <c r="V16" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B17" s="46">
+      <c r="S16" s="43"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="45">
+        <f>IF(T16="","",U16/T16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22">
+      <c r="B17" s="27">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,18,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="42">
-        <v>0</v>
-      </c>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="47">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="45"/>
-      <c r="J17" s="36" t="s">
+      <c r="C17" s="27"/>
+      <c r="D17" s="28">
+        <v>0</v>
+      </c>
+      <c r="E17" s="29"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="31">
+        <f>IFERROR(F17/D17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="32"/>
+      <c r="J17" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="K17" s="37">
+      <c r="K17" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L17" s="38"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36" t="s">
+      <c r="L17" s="43"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="45">
+        <f>IF(M17="","",N17/M17)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="R17" s="37">
+      <c r="R17" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S17" s="38"/>
-      <c r="T17" s="39"/>
-      <c r="U17" s="39"/>
-      <c r="V17" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B18" s="46">
+      <c r="S17" s="43"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="44"/>
+      <c r="V17" s="45">
+        <f>IF(T17="","",U17/T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="27">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,19,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="42">
-        <v>0</v>
-      </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="47">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="45"/>
-      <c r="J18" s="36" t="s">
+      <c r="C18" s="27"/>
+      <c r="D18" s="28">
+        <v>0</v>
+      </c>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31">
+        <f>IFERROR(F18/D18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="32"/>
+      <c r="J18" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="37">
+      <c r="K18" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="38"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="36" t="s">
+      <c r="L18" s="43"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="45">
+        <f>IF(M18="","",N18/M18)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="R18" s="37">
+      <c r="R18" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S18" s="38"/>
-      <c r="T18" s="39"/>
-      <c r="U18" s="39"/>
-      <c r="V18" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B19" s="48">
+      <c r="S18" s="43"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="44"/>
+      <c r="V18" s="45">
+        <f>IF(T18="","",U18/T18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="27">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,20,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="42">
-        <v>0</v>
-      </c>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="47">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="45"/>
-      <c r="J19" s="36" t="s">
+      <c r="C19" s="27"/>
+      <c r="D19" s="28">
+        <v>0</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="31">
+        <f>IFERROR(F19/D19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="32"/>
+      <c r="J19" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L19" s="38"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="36" t="s">
+      <c r="L19" s="43"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="45">
+        <f>IF(M19="","",N19/M19)</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="R19" s="37">
+      <c r="R19" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S19" s="38"/>
-      <c r="T19" s="39"/>
-      <c r="U19" s="39"/>
-      <c r="V19" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B20" s="49">
+      <c r="S19" s="43"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="44"/>
+      <c r="V19" s="45">
+        <f>IF(T19="","",U19/T19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="33">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,21,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="50">
+      <c r="C20" s="33"/>
+      <c r="D20" s="34">
         <f>SUMPRODUCT(ROUND(D15:D19, 2))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="34">
         <f>SUMPRODUCT(ROUND(E15:E19, 2))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="34">
         <f>SUMPRODUCT(ROUND(F15:F19, 2))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="51">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="52"/>
-      <c r="J20" s="36" t="s">
+      <c r="G20" s="35">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="36"/>
+      <c r="J20" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="K20" s="37">
+      <c r="K20" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L20" s="38"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="36" t="s">
+      <c r="L20" s="43"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="45">
+        <f>IF(M20="","",N20/M20)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="37">
+      <c r="R20" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S20" s="38"/>
-      <c r="T20" s="39"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S20" s="43"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="44"/>
+      <c r="V20" s="45">
+        <f>IF(T20="","",U20/T20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="13.5" customHeight="1">
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L21" s="38"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="36" t="s">
+      <c r="L21" s="43"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="45">
+        <f>IF(M21="","",N21/M21)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="R21" s="37">
+      <c r="R21" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S21" s="38"/>
-      <c r="T21" s="39"/>
-      <c r="U21" s="39"/>
-      <c r="V21" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S21" s="43"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="45">
+        <f>IF(T21="","",U21/T21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:22">
-      <c r="J22" s="36" t="s">
+      <c r="J22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L22" s="38"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="36" t="s">
+      <c r="L22" s="43"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="45">
+        <f>IF(M22="","",N22/M22)</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="R22" s="37">
+      <c r="R22" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S22" s="38"/>
-      <c r="T22" s="39"/>
-      <c r="U22" s="39"/>
-      <c r="V22" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:22" ht="13.5" customHeight="1">
-      <c r="B23" s="20"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="22">
+      <c r="S22" s="43"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="44"/>
+      <c r="V22" s="45">
+        <f>IF(T22="","",U22/T22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="37"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="19">
         <f>D11</f>
         <v>0</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="20">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,25,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="19">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,55,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="19">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,56,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="21">
         <f>H11</f>
         <v>0</v>
       </c>
-      <c r="J23" s="36" t="s">
+      <c r="J23" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="K23" s="37">
+      <c r="K23" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="38"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="36" t="s">
+      <c r="L23" s="43"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="45">
+        <f>IF(M23="","",N23/M23)</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="R23" s="37">
+      <c r="R23" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S23" s="38"/>
-      <c r="T23" s="39"/>
-      <c r="U23" s="39"/>
-      <c r="V23" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B24" s="28">
+      <c r="S23" s="43"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="44"/>
+      <c r="V23" s="45">
+        <f>IF(T23="","",U23/T23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="22">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,24,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="24"/>
-      <c r="J24" s="36" t="s">
+      <c r="C24" s="22"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="21"/>
+      <c r="J24" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K24" s="37">
+      <c r="K24" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L24" s="38"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="36" t="s">
+      <c r="L24" s="43"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="45">
+        <f>IF(M24="","",N24/M24)</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="R24" s="37">
+      <c r="R24" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S24" s="38"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B25" s="31">
+      <c r="S24" s="43"/>
+      <c r="T24" s="44"/>
+      <c r="U24" s="44"/>
+      <c r="V24" s="45">
+        <f>IF(T24="","",U24/T24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="23">
         <f>B13</f>
         <v>0</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="24"/>
-      <c r="J25" s="36" t="s">
+      <c r="C25" s="23"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="21"/>
+      <c r="J25" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L25" s="38"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="36" t="s">
+      <c r="L25" s="43"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="45">
+        <f>IF(M25="","",N25/M25)</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="R25" s="37">
+      <c r="R25" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S25" s="38"/>
-      <c r="T25" s="39"/>
-      <c r="U25" s="39"/>
-      <c r="V25" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="24"/>
-      <c r="J26" s="36" t="s">
+      <c r="S25" s="43"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="44"/>
+      <c r="V25" s="45">
+        <f>IF(T25="","",U25/T25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="21"/>
+      <c r="J26" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="38"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="36" t="s">
+      <c r="L26" s="43"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="45">
+        <f>IF(M26="","",N26/M26)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="R26" s="37">
+      <c r="R26" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S26" s="38"/>
-      <c r="T26" s="39"/>
-      <c r="U26" s="39"/>
-      <c r="V26" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:22" ht="12.75" customHeight="1">
-      <c r="B27" s="55" t="s">
+      <c r="S26" s="43"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="45">
+        <f>IF(T26="","",U26/T26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="B27" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="56" t="str">
+      <c r="C27" s="47" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,29,FALSE))</f>
         <v/>
       </c>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="59"/>
-      <c r="J27" s="36" t="s">
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="50"/>
+      <c r="J27" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="K27" s="37">
+      <c r="K27" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L27" s="38"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="36" t="s">
+      <c r="L27" s="43"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="45">
+        <f>IF(M27="","",N27/M27)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="R27" s="37">
+      <c r="R27" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S27" s="38"/>
-      <c r="T27" s="39"/>
-      <c r="U27" s="39"/>
-      <c r="V27" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S27" s="43"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="44"/>
+      <c r="V27" s="45">
+        <f>IF(T27="","",U27/T27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:22">
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="61"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="66"/>
-      <c r="J28" s="36" t="s">
+      <c r="C28" s="52"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="57"/>
+      <c r="J28" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="K28" s="37">
+      <c r="K28" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="38"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="36" t="s">
+      <c r="L28" s="43"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="45">
+        <f>IF(M28="","",N28/M28)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="R28" s="37">
+      <c r="R28" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S28" s="38"/>
-      <c r="T28" s="39"/>
-      <c r="U28" s="39"/>
-      <c r="V28" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S28" s="43"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="44"/>
+      <c r="V28" s="45">
+        <f>IF(T28="","",U28/T28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:22">
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="66"/>
-      <c r="J29" s="36" t="s">
+      <c r="C29" s="52"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="57"/>
+      <c r="J29" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="K29" s="37">
+      <c r="K29" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L29" s="38"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="36" t="s">
+      <c r="L29" s="43"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="45">
+        <f>IF(M29="","",N29/M29)</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="R29" s="37">
+      <c r="R29" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S29" s="38"/>
-      <c r="T29" s="39"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S29" s="43"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="44"/>
+      <c r="V29" s="45">
+        <f>IF(T29="","",U29/T29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:22">
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H30" s="66"/>
-      <c r="J30" s="36" t="s">
+      <c r="C30" s="52"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="57"/>
+      <c r="J30" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L30" s="38"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="36" t="s">
+      <c r="L30" s="43"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="45">
+        <f>IF(M30="","",N30/M30)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="R30" s="37">
+      <c r="R30" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S30" s="38"/>
-      <c r="T30" s="39"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S30" s="43"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="45">
+        <f>IF(T30="","",U30/T30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:22">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H31" s="66"/>
-      <c r="J31" s="53" t="s">
+      <c r="C31" s="52"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="57"/>
+      <c r="J31" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="K31" s="54">
+      <c r="K31" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="38"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="40">
-        <f>IFERROR(INDEX($N$1:$N$31,ROW())/INDEX($M$1:$M$31,ROW()),"")</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="53" t="s">
+      <c r="L31" s="43"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="45">
+        <f>IF(M31="","",N31/M31)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="R31" s="54">
+      <c r="R31" s="42">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,23,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="S31" s="38"/>
-      <c r="T31" s="39"/>
-      <c r="U31" s="39"/>
-      <c r="V31" s="40">
-        <f>IFERROR(INDEX($U$1:$U$31,ROW())/INDEX($T$1:$T$31,ROW()),"")</f>
+      <c r="S31" s="43"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="45">
+        <f>IF(T31="","",U31/T31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:22">
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H32" s="66"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="57"/>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="61"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H33" s="66"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="57"/>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="60" t="s">
+      <c r="B34" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="61"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H34" s="66"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="57"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="60" t="s">
+      <c r="B35" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="61"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H35" s="66"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="57"/>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="60" t="s">
+      <c r="B36" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="61"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H36" s="66"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H36" s="57"/>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="61"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H37" s="66"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="57"/>
     </row>
     <row r="38" spans="2:8">
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H38" s="66"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="57"/>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="61"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H39" s="66"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="57"/>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="61"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H40" s="66"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H40" s="57"/>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="61"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H41" s="66"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H41" s="57"/>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="60" t="s">
+      <c r="B42" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="61"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H42" s="66"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H42" s="57"/>
     </row>
     <row r="43" spans="2:8">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="61"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="63"/>
-      <c r="F43" s="64"/>
-      <c r="G43" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H43" s="66"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H43" s="57"/>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="60" t="s">
+      <c r="B44" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="61"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H44" s="66"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H44" s="57"/>
     </row>
     <row r="45" spans="2:8">
-      <c r="B45" s="60" t="s">
+      <c r="B45" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="C45" s="61"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H45" s="66"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="57"/>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="60" t="s">
+      <c r="B46" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="61"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H46" s="66"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H46" s="57"/>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="60" t="s">
+      <c r="B47" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="61"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="63"/>
-      <c r="F47" s="64"/>
-      <c r="G47" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H47" s="66"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H47" s="57"/>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="67" t="str">
+      <c r="B48" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,30,FALSE))</f>
         <v/>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="69" t="str">
+      <c r="C48" s="59"/>
+      <c r="D48" s="60" t="str">
         <f>SUMPRODUCT(ROUND(D28:D47,2))</f>
         <v/>
       </c>
-      <c r="E48" s="69" t="str">
+      <c r="E48" s="60" t="str">
         <f>SUMPRODUCT(ROUND(E28:E47,2))</f>
         <v/>
       </c>
-      <c r="F48" s="69" t="str">
+      <c r="F48" s="60" t="str">
         <f>SUMPRODUCT(ROUND(F28:F47,2))</f>
         <v/>
       </c>
-      <c r="G48" s="70" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H48" s="71"/>
+      <c r="G48" s="61" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="62"/>
     </row>
     <row r="49" spans="2:8">
-      <c r="B49" s="55" t="s">
+      <c r="B49" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="56" t="str">
+      <c r="C49" s="47" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,31,FALSE))</f>
         <v/>
       </c>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="59"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="50"/>
     </row>
     <row r="50" spans="2:8">
-      <c r="B50" s="60" t="s">
+      <c r="B50" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="61"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="63"/>
-      <c r="F50" s="64"/>
-      <c r="G50" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H50" s="66"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H50" s="57"/>
     </row>
     <row r="51" spans="2:8">
-      <c r="B51" s="60" t="s">
+      <c r="B51" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="61"/>
-      <c r="D51" s="62"/>
-      <c r="E51" s="63"/>
-      <c r="F51" s="64"/>
-      <c r="G51" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H51" s="66"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H51" s="57"/>
     </row>
     <row r="52" spans="2:8">
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="C52" s="61"/>
-      <c r="D52" s="62"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="64"/>
-      <c r="G52" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H52" s="66"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H52" s="57"/>
     </row>
     <row r="53" spans="2:8">
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="61"/>
-      <c r="D53" s="62"/>
-      <c r="E53" s="63"/>
-      <c r="F53" s="64"/>
-      <c r="G53" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H53" s="66"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H53" s="57"/>
     </row>
     <row r="54" spans="2:8">
-      <c r="B54" s="60" t="s">
+      <c r="B54" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="61"/>
-      <c r="D54" s="62"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="64"/>
-      <c r="G54" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H54" s="66"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H54" s="57"/>
     </row>
     <row r="55" spans="2:8">
-      <c r="B55" s="60" t="s">
+      <c r="B55" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="61"/>
-      <c r="D55" s="62"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H55" s="66"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H55" s="57"/>
     </row>
     <row r="56" spans="2:8">
-      <c r="B56" s="60" t="s">
+      <c r="B56" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="C56" s="61"/>
-      <c r="D56" s="62"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H56" s="66"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H56" s="57"/>
     </row>
     <row r="57" spans="2:8">
-      <c r="B57" s="60" t="s">
+      <c r="B57" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="61"/>
-      <c r="D57" s="62"/>
-      <c r="E57" s="63"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H57" s="66"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H57" s="57"/>
     </row>
     <row r="58" spans="2:8">
-      <c r="B58" s="60" t="s">
+      <c r="B58" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="61"/>
-      <c r="D58" s="62"/>
-      <c r="E58" s="63"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H58" s="66"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H58" s="57"/>
     </row>
     <row r="59" spans="2:8">
-      <c r="B59" s="60" t="s">
+      <c r="B59" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C59" s="61"/>
-      <c r="D59" s="62"/>
-      <c r="E59" s="63"/>
-      <c r="F59" s="64"/>
-      <c r="G59" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H59" s="66"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H59" s="57"/>
     </row>
     <row r="60" spans="2:8">
-      <c r="B60" s="60" t="s">
+      <c r="B60" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="61"/>
-      <c r="D60" s="62"/>
-      <c r="E60" s="63"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H60" s="66"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H60" s="57"/>
     </row>
     <row r="61" spans="2:8">
-      <c r="B61" s="60" t="s">
+      <c r="B61" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C61" s="61"/>
-      <c r="D61" s="62"/>
-      <c r="E61" s="63"/>
-      <c r="F61" s="64"/>
-      <c r="G61" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H61" s="66"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="53"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="55"/>
+      <c r="G61" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H61" s="57"/>
     </row>
     <row r="62" spans="2:8">
-      <c r="B62" s="60" t="s">
+      <c r="B62" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="C62" s="61"/>
-      <c r="D62" s="62"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="64"/>
-      <c r="G62" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H62" s="66"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="55"/>
+      <c r="G62" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H62" s="57"/>
     </row>
     <row r="63" spans="2:8">
-      <c r="B63" s="60" t="s">
+      <c r="B63" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="C63" s="61"/>
-      <c r="D63" s="62"/>
-      <c r="E63" s="63"/>
-      <c r="F63" s="64"/>
-      <c r="G63" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H63" s="66"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="55"/>
+      <c r="G63" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H63" s="57"/>
     </row>
     <row r="64" spans="2:8">
-      <c r="B64" s="60" t="s">
+      <c r="B64" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="61"/>
-      <c r="D64" s="62"/>
-      <c r="E64" s="63"/>
-      <c r="F64" s="64"/>
-      <c r="G64" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H64" s="66"/>
+      <c r="C64" s="52"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H64" s="57"/>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C65" s="61"/>
-      <c r="D65" s="62"/>
-      <c r="E65" s="63"/>
-      <c r="F65" s="64"/>
-      <c r="G65" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H65" s="66"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="53"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H65" s="57"/>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="60" t="s">
+      <c r="B66" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C66" s="61"/>
-      <c r="D66" s="62"/>
-      <c r="E66" s="63"/>
-      <c r="F66" s="64"/>
-      <c r="G66" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H66" s="66"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="53"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="55"/>
+      <c r="G66" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H66" s="57"/>
     </row>
     <row r="67" spans="2:8">
-      <c r="B67" s="60" t="s">
+      <c r="B67" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="61"/>
-      <c r="D67" s="62"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="64"/>
-      <c r="G67" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H67" s="66"/>
+      <c r="C67" s="52"/>
+      <c r="D67" s="53"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="55"/>
+      <c r="G67" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H67" s="57"/>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="60" t="s">
+      <c r="B68" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="61"/>
-      <c r="D68" s="62"/>
-      <c r="E68" s="63"/>
-      <c r="F68" s="64"/>
-      <c r="G68" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H68" s="66"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H68" s="57"/>
     </row>
     <row r="69" spans="2:8">
-      <c r="B69" s="60" t="s">
+      <c r="B69" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C69" s="61"/>
-      <c r="D69" s="62"/>
-      <c r="E69" s="63"/>
-      <c r="F69" s="64"/>
-      <c r="G69" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H69" s="66"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="53"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="55"/>
+      <c r="G69" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H69" s="57"/>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="67" t="str">
+      <c r="B70" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,32,FALSE))</f>
         <v/>
       </c>
-      <c r="C70" s="68"/>
-      <c r="D70" s="69" t="str">
+      <c r="C70" s="59"/>
+      <c r="D70" s="60" t="str">
         <f>SUMPRODUCT(ROUND(D50:D69,2))</f>
         <v/>
       </c>
-      <c r="E70" s="69" t="str">
+      <c r="E70" s="60" t="str">
         <f>SUMPRODUCT(ROUND(E50:E69,2))</f>
         <v/>
       </c>
-      <c r="F70" s="69" t="str">
+      <c r="F70" s="60" t="str">
         <f>SUMPRODUCT(ROUND(F50:F69,2))</f>
         <v/>
       </c>
-      <c r="G70" s="70" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H70" s="71"/>
+      <c r="G70" s="61" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H70" s="62"/>
     </row>
     <row r="71" spans="2:8">
-      <c r="B71" s="55" t="s">
+      <c r="B71" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="56" t="str">
+      <c r="C71" s="47" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,33,FALSE))</f>
         <v/>
       </c>
-      <c r="D71" s="57"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="59"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="50"/>
     </row>
     <row r="72" spans="2:8">
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="C72" s="61"/>
-      <c r="D72" s="62"/>
-      <c r="E72" s="63"/>
-      <c r="F72" s="64"/>
-      <c r="G72" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H72" s="66"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H72" s="57"/>
     </row>
     <row r="73" spans="2:8">
-      <c r="B73" s="60" t="s">
+      <c r="B73" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C73" s="61"/>
-      <c r="D73" s="62"/>
-      <c r="E73" s="63"/>
-      <c r="F73" s="64"/>
-      <c r="G73" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H73" s="66"/>
+      <c r="C73" s="52"/>
+      <c r="D73" s="53"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="55"/>
+      <c r="G73" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H73" s="57"/>
     </row>
     <row r="74" spans="2:8">
-      <c r="B74" s="60" t="s">
+      <c r="B74" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="C74" s="61"/>
-      <c r="D74" s="62"/>
-      <c r="E74" s="63"/>
-      <c r="F74" s="64"/>
-      <c r="G74" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H74" s="66"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="55"/>
+      <c r="G74" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H74" s="57"/>
     </row>
     <row r="75" spans="2:8">
-      <c r="B75" s="60" t="s">
+      <c r="B75" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="C75" s="61"/>
-      <c r="D75" s="62"/>
-      <c r="E75" s="63"/>
-      <c r="F75" s="64"/>
-      <c r="G75" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H75" s="66"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="54"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H75" s="57"/>
     </row>
     <row r="76" spans="2:8">
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="C76" s="61"/>
-      <c r="D76" s="62"/>
-      <c r="E76" s="63"/>
-      <c r="F76" s="64"/>
-      <c r="G76" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H76" s="66"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="55"/>
+      <c r="G76" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H76" s="57"/>
     </row>
     <row r="77" spans="2:8">
-      <c r="B77" s="60" t="s">
+      <c r="B77" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="C77" s="61"/>
-      <c r="D77" s="62"/>
-      <c r="E77" s="63"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H77" s="66"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="53"/>
+      <c r="E77" s="54"/>
+      <c r="F77" s="55"/>
+      <c r="G77" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H77" s="57"/>
     </row>
     <row r="78" spans="2:8">
-      <c r="B78" s="60" t="s">
+      <c r="B78" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="C78" s="61"/>
-      <c r="D78" s="62"/>
-      <c r="E78" s="63"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H78" s="66"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="55"/>
+      <c r="G78" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H78" s="57"/>
     </row>
     <row r="79" spans="2:8">
-      <c r="B79" s="60" t="s">
+      <c r="B79" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="C79" s="61"/>
-      <c r="D79" s="62"/>
-      <c r="E79" s="63"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H79" s="66"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="55"/>
+      <c r="G79" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H79" s="57"/>
     </row>
     <row r="80" spans="2:8">
-      <c r="B80" s="60" t="s">
+      <c r="B80" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="C80" s="61"/>
-      <c r="D80" s="62"/>
-      <c r="E80" s="63"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H80" s="66"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="55"/>
+      <c r="G80" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H80" s="57"/>
     </row>
     <row r="81" spans="2:8">
-      <c r="B81" s="60" t="s">
+      <c r="B81" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="C81" s="61"/>
-      <c r="D81" s="62"/>
-      <c r="E81" s="63"/>
-      <c r="F81" s="64"/>
-      <c r="G81" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H81" s="66"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="53"/>
+      <c r="E81" s="54"/>
+      <c r="F81" s="55"/>
+      <c r="G81" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H81" s="57"/>
     </row>
     <row r="82" spans="2:8">
-      <c r="B82" s="60" t="s">
+      <c r="B82" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="C82" s="61"/>
-      <c r="D82" s="62"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="64"/>
-      <c r="G82" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H82" s="66"/>
+      <c r="C82" s="52"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="55"/>
+      <c r="G82" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H82" s="57"/>
     </row>
     <row r="83" spans="2:8">
-      <c r="B83" s="60" t="s">
+      <c r="B83" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="C83" s="61"/>
-      <c r="D83" s="62"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="64"/>
-      <c r="G83" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H83" s="66"/>
+      <c r="C83" s="52"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="55"/>
+      <c r="G83" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H83" s="57"/>
     </row>
     <row r="84" spans="2:8">
-      <c r="B84" s="60" t="s">
+      <c r="B84" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="C84" s="61"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="63"/>
-      <c r="F84" s="64"/>
-      <c r="G84" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H84" s="66"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="53"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H84" s="57"/>
     </row>
     <row r="85" spans="2:8">
-      <c r="B85" s="60" t="s">
+      <c r="B85" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="C85" s="61"/>
-      <c r="D85" s="62"/>
-      <c r="E85" s="63"/>
-      <c r="F85" s="64"/>
-      <c r="G85" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H85" s="66"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="54"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H85" s="57"/>
     </row>
     <row r="86" spans="2:8">
-      <c r="B86" s="60" t="s">
+      <c r="B86" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="C86" s="61"/>
-      <c r="D86" s="62"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="64"/>
-      <c r="G86" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H86" s="66"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H86" s="57"/>
     </row>
     <row r="87" spans="2:8">
-      <c r="B87" s="60" t="s">
+      <c r="B87" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="C87" s="61"/>
-      <c r="D87" s="62"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="64"/>
-      <c r="G87" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H87" s="66"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="55"/>
+      <c r="G87" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H87" s="57"/>
     </row>
     <row r="88" spans="2:8">
-      <c r="B88" s="60" t="s">
+      <c r="B88" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="C88" s="61"/>
-      <c r="D88" s="62"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="64"/>
-      <c r="G88" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H88" s="66"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="55"/>
+      <c r="G88" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H88" s="57"/>
     </row>
     <row r="89" spans="2:8">
-      <c r="B89" s="60" t="s">
+      <c r="B89" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="61"/>
-      <c r="D89" s="62"/>
-      <c r="E89" s="63"/>
-      <c r="F89" s="64"/>
-      <c r="G89" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H89" s="66"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="55"/>
+      <c r="G89" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H89" s="57"/>
     </row>
     <row r="90" spans="2:8">
-      <c r="B90" s="60" t="s">
+      <c r="B90" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="C90" s="61"/>
-      <c r="D90" s="62"/>
-      <c r="E90" s="63"/>
-      <c r="F90" s="64"/>
-      <c r="G90" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H90" s="66"/>
+      <c r="C90" s="52"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="54"/>
+      <c r="F90" s="55"/>
+      <c r="G90" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H90" s="57"/>
     </row>
     <row r="91" spans="2:8">
-      <c r="B91" s="60" t="s">
+      <c r="B91" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="C91" s="61"/>
-      <c r="D91" s="62"/>
-      <c r="E91" s="63"/>
-      <c r="F91" s="64"/>
-      <c r="G91" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H91" s="66"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="53"/>
+      <c r="E91" s="54"/>
+      <c r="F91" s="55"/>
+      <c r="G91" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H91" s="57"/>
     </row>
     <row r="92" spans="2:8">
-      <c r="B92" s="60" t="s">
+      <c r="B92" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C92" s="61"/>
-      <c r="D92" s="62"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="64"/>
-      <c r="G92" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H92" s="66"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="53"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H92" s="57"/>
     </row>
     <row r="93" spans="2:8">
-      <c r="B93" s="60" t="s">
+      <c r="B93" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C93" s="61"/>
-      <c r="D93" s="62"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="64"/>
-      <c r="G93" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H93" s="66"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="53"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H93" s="57"/>
     </row>
     <row r="94" spans="2:8">
-      <c r="B94" s="60" t="s">
+      <c r="B94" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="C94" s="61"/>
-      <c r="D94" s="62"/>
-      <c r="E94" s="63"/>
-      <c r="F94" s="64"/>
-      <c r="G94" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H94" s="66"/>
+      <c r="C94" s="52"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H94" s="57"/>
     </row>
     <row r="95" spans="2:8">
-      <c r="B95" s="60" t="s">
+      <c r="B95" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="C95" s="61"/>
-      <c r="D95" s="62"/>
-      <c r="E95" s="63"/>
-      <c r="F95" s="64"/>
-      <c r="G95" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H95" s="66"/>
+      <c r="C95" s="52"/>
+      <c r="D95" s="53"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H95" s="57"/>
     </row>
     <row r="96" spans="2:8">
-      <c r="B96" s="60" t="s">
+      <c r="B96" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="C96" s="61"/>
-      <c r="D96" s="62"/>
-      <c r="E96" s="63"/>
-      <c r="F96" s="64"/>
-      <c r="G96" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H96" s="66"/>
+      <c r="C96" s="52"/>
+      <c r="D96" s="53"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H96" s="57"/>
     </row>
     <row r="97" spans="2:8">
-      <c r="B97" s="60" t="s">
+      <c r="B97" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="C97" s="61"/>
-      <c r="D97" s="62"/>
-      <c r="E97" s="63"/>
-      <c r="F97" s="64"/>
-      <c r="G97" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H97" s="66"/>
+      <c r="C97" s="52"/>
+      <c r="D97" s="53"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H97" s="57"/>
     </row>
     <row r="98" spans="2:8">
-      <c r="B98" s="60" t="s">
+      <c r="B98" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="C98" s="61"/>
-      <c r="D98" s="62"/>
-      <c r="E98" s="63"/>
-      <c r="F98" s="64"/>
-      <c r="G98" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H98" s="66"/>
+      <c r="C98" s="52"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H98" s="57"/>
     </row>
     <row r="99" spans="2:8">
-      <c r="B99" s="60" t="s">
+      <c r="B99" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="C99" s="61"/>
-      <c r="D99" s="62"/>
-      <c r="E99" s="63"/>
-      <c r="F99" s="64"/>
-      <c r="G99" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H99" s="66"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="53"/>
+      <c r="E99" s="54"/>
+      <c r="F99" s="55"/>
+      <c r="G99" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H99" s="57"/>
     </row>
     <row r="100" spans="2:8">
-      <c r="B100" s="60" t="s">
+      <c r="B100" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="C100" s="61"/>
-      <c r="D100" s="62"/>
-      <c r="E100" s="63"/>
-      <c r="F100" s="64"/>
-      <c r="G100" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H100" s="66"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="53"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="55"/>
+      <c r="G100" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H100" s="57"/>
     </row>
     <row r="101" spans="2:8">
-      <c r="B101" s="60" t="s">
+      <c r="B101" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="C101" s="61"/>
-      <c r="D101" s="62"/>
-      <c r="E101" s="63"/>
-      <c r="F101" s="64"/>
-      <c r="G101" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H101" s="66"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="53"/>
+      <c r="E101" s="54"/>
+      <c r="F101" s="55"/>
+      <c r="G101" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H101" s="57"/>
     </row>
     <row r="102" spans="2:8">
-      <c r="B102" s="67" t="str">
+      <c r="B102" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,34,FALSE))</f>
         <v/>
       </c>
-      <c r="C102" s="68"/>
-      <c r="D102" s="69" t="str">
+      <c r="C102" s="59"/>
+      <c r="D102" s="60" t="str">
         <f>SUMPRODUCT(ROUND(D72:D101,2))</f>
         <v/>
       </c>
-      <c r="E102" s="69" t="str">
+      <c r="E102" s="60" t="str">
         <f>SUMPRODUCT(ROUND(E72:E101,2))</f>
         <v/>
       </c>
-      <c r="F102" s="69" t="str">
+      <c r="F102" s="60" t="str">
         <f>SUMPRODUCT(ROUND(F72:F101,2))</f>
         <v/>
       </c>
-      <c r="G102" s="70" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H102" s="71"/>
+      <c r="G102" s="61" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H102" s="62"/>
     </row>
     <row r="103" spans="2:8">
-      <c r="B103" s="55" t="s">
+      <c r="B103" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="C103" s="56" t="str">
+      <c r="C103" s="47" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,35,FALSE))</f>
         <v/>
       </c>
-      <c r="D103" s="57"/>
-      <c r="E103" s="57"/>
-      <c r="F103" s="57"/>
-      <c r="G103" s="58"/>
-      <c r="H103" s="59"/>
+      <c r="D103" s="48"/>
+      <c r="E103" s="48"/>
+      <c r="F103" s="48"/>
+      <c r="G103" s="49"/>
+      <c r="H103" s="50"/>
     </row>
     <row r="104" spans="2:8">
-      <c r="B104" s="60" t="s">
+      <c r="B104" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="C104" s="61"/>
-      <c r="D104" s="62"/>
-      <c r="E104" s="63"/>
-      <c r="F104" s="64"/>
-      <c r="G104" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H104" s="66"/>
+      <c r="C104" s="52"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H104" s="57"/>
     </row>
     <row r="105" spans="2:8">
-      <c r="B105" s="60" t="s">
+      <c r="B105" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="C105" s="61"/>
-      <c r="D105" s="62"/>
-      <c r="E105" s="63"/>
-      <c r="F105" s="64"/>
-      <c r="G105" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H105" s="66"/>
+      <c r="C105" s="52"/>
+      <c r="D105" s="53"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H105" s="57"/>
     </row>
     <row r="106" spans="2:8">
-      <c r="B106" s="60" t="s">
+      <c r="B106" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="C106" s="61"/>
-      <c r="D106" s="62"/>
-      <c r="E106" s="63"/>
-      <c r="F106" s="64"/>
-      <c r="G106" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H106" s="66"/>
+      <c r="C106" s="52"/>
+      <c r="D106" s="53"/>
+      <c r="E106" s="54"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H106" s="57"/>
     </row>
     <row r="107" spans="2:8">
-      <c r="B107" s="60" t="s">
+      <c r="B107" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="C107" s="61"/>
-      <c r="D107" s="62"/>
-      <c r="E107" s="63"/>
-      <c r="F107" s="64"/>
-      <c r="G107" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H107" s="66"/>
+      <c r="C107" s="52"/>
+      <c r="D107" s="53"/>
+      <c r="E107" s="54"/>
+      <c r="F107" s="55"/>
+      <c r="G107" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H107" s="57"/>
     </row>
     <row r="108" spans="2:8">
-      <c r="B108" s="60" t="s">
+      <c r="B108" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="C108" s="61"/>
-      <c r="D108" s="62"/>
-      <c r="E108" s="63"/>
-      <c r="F108" s="64"/>
-      <c r="G108" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H108" s="66"/>
+      <c r="C108" s="52"/>
+      <c r="D108" s="53"/>
+      <c r="E108" s="54"/>
+      <c r="F108" s="55"/>
+      <c r="G108" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H108" s="57"/>
     </row>
     <row r="109" spans="2:8">
-      <c r="B109" s="60" t="s">
+      <c r="B109" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="C109" s="61"/>
-      <c r="D109" s="62"/>
-      <c r="E109" s="63"/>
-      <c r="F109" s="64"/>
-      <c r="G109" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H109" s="66"/>
+      <c r="C109" s="52"/>
+      <c r="D109" s="53"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="55"/>
+      <c r="G109" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H109" s="57"/>
     </row>
     <row r="110" spans="2:8">
-      <c r="B110" s="60" t="s">
+      <c r="B110" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="C110" s="61"/>
-      <c r="D110" s="62"/>
-      <c r="E110" s="63"/>
-      <c r="F110" s="64"/>
-      <c r="G110" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H110" s="66"/>
+      <c r="C110" s="52"/>
+      <c r="D110" s="53"/>
+      <c r="E110" s="54"/>
+      <c r="F110" s="55"/>
+      <c r="G110" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H110" s="57"/>
     </row>
     <row r="111" spans="2:8">
-      <c r="B111" s="60" t="s">
+      <c r="B111" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="C111" s="61"/>
-      <c r="D111" s="62"/>
-      <c r="E111" s="63"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H111" s="66"/>
+      <c r="C111" s="52"/>
+      <c r="D111" s="53"/>
+      <c r="E111" s="54"/>
+      <c r="F111" s="55"/>
+      <c r="G111" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H111" s="57"/>
     </row>
     <row r="112" spans="2:8">
-      <c r="B112" s="60" t="s">
+      <c r="B112" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="C112" s="61"/>
-      <c r="D112" s="62"/>
-      <c r="E112" s="63"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H112" s="66"/>
+      <c r="C112" s="52"/>
+      <c r="D112" s="53"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="55"/>
+      <c r="G112" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H112" s="57"/>
     </row>
     <row r="113" spans="2:8">
-      <c r="B113" s="60" t="s">
+      <c r="B113" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="C113" s="61"/>
-      <c r="D113" s="62"/>
-      <c r="E113" s="63"/>
-      <c r="F113" s="64"/>
-      <c r="G113" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H113" s="66"/>
+      <c r="C113" s="52"/>
+      <c r="D113" s="53"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="55"/>
+      <c r="G113" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H113" s="57"/>
     </row>
     <row r="114" spans="2:8">
-      <c r="B114" s="60" t="s">
+      <c r="B114" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="C114" s="61"/>
-      <c r="D114" s="62"/>
-      <c r="E114" s="63"/>
-      <c r="F114" s="64"/>
-      <c r="G114" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H114" s="66"/>
+      <c r="C114" s="52"/>
+      <c r="D114" s="53"/>
+      <c r="E114" s="54"/>
+      <c r="F114" s="55"/>
+      <c r="G114" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H114" s="57"/>
     </row>
     <row r="115" spans="2:8">
-      <c r="B115" s="60" t="s">
+      <c r="B115" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="C115" s="61"/>
-      <c r="D115" s="62"/>
-      <c r="E115" s="63"/>
-      <c r="F115" s="64"/>
-      <c r="G115" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H115" s="66"/>
+      <c r="C115" s="52"/>
+      <c r="D115" s="53"/>
+      <c r="E115" s="54"/>
+      <c r="F115" s="55"/>
+      <c r="G115" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H115" s="57"/>
     </row>
     <row r="116" spans="2:8">
-      <c r="B116" s="60" t="s">
+      <c r="B116" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="C116" s="61"/>
-      <c r="D116" s="62"/>
-      <c r="E116" s="63"/>
-      <c r="F116" s="64"/>
-      <c r="G116" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H116" s="66"/>
+      <c r="C116" s="52"/>
+      <c r="D116" s="53"/>
+      <c r="E116" s="54"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H116" s="57"/>
     </row>
     <row r="117" spans="2:8">
-      <c r="B117" s="60" t="s">
+      <c r="B117" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="C117" s="61"/>
-      <c r="D117" s="62"/>
-      <c r="E117" s="63"/>
-      <c r="F117" s="64"/>
-      <c r="G117" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H117" s="66"/>
+      <c r="C117" s="52"/>
+      <c r="D117" s="53"/>
+      <c r="E117" s="54"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H117" s="57"/>
     </row>
     <row r="118" spans="2:8">
-      <c r="B118" s="60" t="s">
+      <c r="B118" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="C118" s="61"/>
-      <c r="D118" s="62"/>
-      <c r="E118" s="63"/>
-      <c r="F118" s="64"/>
-      <c r="G118" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H118" s="66"/>
+      <c r="C118" s="52"/>
+      <c r="D118" s="53"/>
+      <c r="E118" s="54"/>
+      <c r="F118" s="55"/>
+      <c r="G118" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H118" s="57"/>
     </row>
     <row r="119" spans="2:8">
-      <c r="B119" s="60" t="s">
+      <c r="B119" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="C119" s="61"/>
-      <c r="D119" s="62"/>
-      <c r="E119" s="63"/>
-      <c r="F119" s="64"/>
-      <c r="G119" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H119" s="66"/>
+      <c r="C119" s="52"/>
+      <c r="D119" s="53"/>
+      <c r="E119" s="54"/>
+      <c r="F119" s="55"/>
+      <c r="G119" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H119" s="57"/>
     </row>
     <row r="120" spans="2:8">
-      <c r="B120" s="60" t="s">
+      <c r="B120" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="C120" s="61"/>
-      <c r="D120" s="62"/>
-      <c r="E120" s="63"/>
-      <c r="F120" s="64"/>
-      <c r="G120" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H120" s="66"/>
+      <c r="C120" s="52"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="54"/>
+      <c r="F120" s="55"/>
+      <c r="G120" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H120" s="57"/>
     </row>
     <row r="121" spans="2:8">
-      <c r="B121" s="60" t="s">
+      <c r="B121" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="C121" s="61"/>
-      <c r="D121" s="62"/>
-      <c r="E121" s="63"/>
-      <c r="F121" s="64"/>
-      <c r="G121" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H121" s="66"/>
+      <c r="C121" s="52"/>
+      <c r="D121" s="53"/>
+      <c r="E121" s="54"/>
+      <c r="F121" s="55"/>
+      <c r="G121" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H121" s="57"/>
     </row>
     <row r="122" spans="2:8">
-      <c r="B122" s="60" t="s">
+      <c r="B122" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="C122" s="61"/>
-      <c r="D122" s="62"/>
-      <c r="E122" s="63"/>
-      <c r="F122" s="64"/>
-      <c r="G122" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H122" s="66"/>
+      <c r="C122" s="52"/>
+      <c r="D122" s="53"/>
+      <c r="E122" s="54"/>
+      <c r="F122" s="55"/>
+      <c r="G122" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H122" s="57"/>
     </row>
     <row r="123" spans="2:8">
-      <c r="B123" s="60" t="s">
+      <c r="B123" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="C123" s="61"/>
-      <c r="D123" s="62"/>
-      <c r="E123" s="63"/>
-      <c r="F123" s="64"/>
-      <c r="G123" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H123" s="66"/>
+      <c r="C123" s="52"/>
+      <c r="D123" s="53"/>
+      <c r="E123" s="54"/>
+      <c r="F123" s="55"/>
+      <c r="G123" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H123" s="57"/>
     </row>
     <row r="124" spans="2:8">
-      <c r="B124" s="60" t="s">
+      <c r="B124" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="C124" s="61"/>
-      <c r="D124" s="62"/>
-      <c r="E124" s="63"/>
-      <c r="F124" s="64"/>
-      <c r="G124" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H124" s="66"/>
+      <c r="C124" s="52"/>
+      <c r="D124" s="53"/>
+      <c r="E124" s="54"/>
+      <c r="F124" s="55"/>
+      <c r="G124" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H124" s="57"/>
     </row>
     <row r="125" spans="2:8">
-      <c r="B125" s="60" t="s">
+      <c r="B125" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="C125" s="61"/>
-      <c r="D125" s="62"/>
-      <c r="E125" s="63"/>
-      <c r="F125" s="64"/>
-      <c r="G125" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H125" s="66"/>
+      <c r="C125" s="52"/>
+      <c r="D125" s="53"/>
+      <c r="E125" s="54"/>
+      <c r="F125" s="55"/>
+      <c r="G125" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H125" s="57"/>
     </row>
     <row r="126" spans="2:8">
-      <c r="B126" s="60" t="s">
+      <c r="B126" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="C126" s="61"/>
-      <c r="D126" s="62"/>
-      <c r="E126" s="63"/>
-      <c r="F126" s="64"/>
-      <c r="G126" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H126" s="66"/>
+      <c r="C126" s="52"/>
+      <c r="D126" s="53"/>
+      <c r="E126" s="54"/>
+      <c r="F126" s="55"/>
+      <c r="G126" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H126" s="57"/>
     </row>
     <row r="127" spans="2:8">
-      <c r="B127" s="60" t="s">
+      <c r="B127" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="C127" s="61"/>
-      <c r="D127" s="62"/>
-      <c r="E127" s="63"/>
-      <c r="F127" s="64"/>
-      <c r="G127" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H127" s="66"/>
+      <c r="C127" s="52"/>
+      <c r="D127" s="53"/>
+      <c r="E127" s="54"/>
+      <c r="F127" s="55"/>
+      <c r="G127" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H127" s="57"/>
     </row>
     <row r="128" spans="2:8">
-      <c r="B128" s="60" t="s">
+      <c r="B128" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="C128" s="61"/>
-      <c r="D128" s="62"/>
-      <c r="E128" s="63"/>
-      <c r="F128" s="64"/>
-      <c r="G128" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H128" s="66"/>
+      <c r="C128" s="52"/>
+      <c r="D128" s="53"/>
+      <c r="E128" s="54"/>
+      <c r="F128" s="55"/>
+      <c r="G128" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H128" s="57"/>
     </row>
     <row r="129" spans="2:8">
-      <c r="B129" s="60" t="s">
+      <c r="B129" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="C129" s="61"/>
-      <c r="D129" s="62"/>
-      <c r="E129" s="63"/>
-      <c r="F129" s="64"/>
-      <c r="G129" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H129" s="66"/>
+      <c r="C129" s="52"/>
+      <c r="D129" s="53"/>
+      <c r="E129" s="54"/>
+      <c r="F129" s="55"/>
+      <c r="G129" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H129" s="57"/>
     </row>
     <row r="130" spans="2:8">
-      <c r="B130" s="60" t="s">
+      <c r="B130" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="C130" s="61"/>
-      <c r="D130" s="62"/>
-      <c r="E130" s="63"/>
-      <c r="F130" s="64"/>
-      <c r="G130" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H130" s="66"/>
+      <c r="C130" s="52"/>
+      <c r="D130" s="53"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="55"/>
+      <c r="G130" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H130" s="57"/>
     </row>
     <row r="131" spans="2:8">
-      <c r="B131" s="60" t="s">
+      <c r="B131" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="C131" s="61"/>
-      <c r="D131" s="62"/>
-      <c r="E131" s="63"/>
-      <c r="F131" s="64"/>
-      <c r="G131" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H131" s="66"/>
+      <c r="C131" s="52"/>
+      <c r="D131" s="53"/>
+      <c r="E131" s="54"/>
+      <c r="F131" s="55"/>
+      <c r="G131" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H131" s="57"/>
     </row>
     <row r="132" spans="2:8">
-      <c r="B132" s="60" t="s">
+      <c r="B132" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="C132" s="61"/>
-      <c r="D132" s="62"/>
-      <c r="E132" s="63"/>
-      <c r="F132" s="64"/>
-      <c r="G132" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H132" s="66"/>
+      <c r="C132" s="52"/>
+      <c r="D132" s="53"/>
+      <c r="E132" s="54"/>
+      <c r="F132" s="55"/>
+      <c r="G132" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H132" s="57"/>
     </row>
     <row r="133" spans="2:8">
-      <c r="B133" s="60" t="s">
+      <c r="B133" s="51" t="s">
         <v>142</v>
       </c>
-      <c r="C133" s="61"/>
-      <c r="D133" s="62"/>
-      <c r="E133" s="63"/>
-      <c r="F133" s="64"/>
-      <c r="G133" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H133" s="66"/>
+      <c r="C133" s="52"/>
+      <c r="D133" s="53"/>
+      <c r="E133" s="54"/>
+      <c r="F133" s="55"/>
+      <c r="G133" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H133" s="57"/>
     </row>
     <row r="134" spans="2:8">
-      <c r="B134" s="67" t="str">
+      <c r="B134" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,36,FALSE))</f>
         <v/>
       </c>
-      <c r="C134" s="68"/>
-      <c r="D134" s="69" t="str">
+      <c r="C134" s="59"/>
+      <c r="D134" s="60" t="str">
         <f>SUMPRODUCT(ROUND(D104:D133,2))</f>
         <v/>
       </c>
-      <c r="E134" s="69" t="str">
+      <c r="E134" s="60" t="str">
         <f>SUMPRODUCT(ROUND(E104:E133,2))</f>
         <v/>
       </c>
-      <c r="F134" s="69" t="str">
+      <c r="F134" s="60" t="str">
         <f>SUMPRODUCT(ROUND(F104:F133,2))</f>
         <v/>
       </c>
-      <c r="G134" s="70" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H134" s="71"/>
+      <c r="G134" s="61" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H134" s="62"/>
     </row>
     <row r="135" spans="2:8">
-      <c r="B135" s="55" t="s">
+      <c r="B135" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="C135" s="56" t="str">
+      <c r="C135" s="47" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,37,FALSE))</f>
         <v/>
       </c>
-      <c r="D135" s="57"/>
-      <c r="E135" s="57"/>
-      <c r="F135" s="57"/>
-      <c r="G135" s="58"/>
-      <c r="H135" s="59"/>
+      <c r="D135" s="48"/>
+      <c r="E135" s="48"/>
+      <c r="F135" s="48"/>
+      <c r="G135" s="49"/>
+      <c r="H135" s="50"/>
     </row>
     <row r="136" spans="2:8">
-      <c r="B136" s="60" t="s">
+      <c r="B136" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="C136" s="61"/>
-      <c r="D136" s="62"/>
-      <c r="E136" s="63"/>
-      <c r="F136" s="64"/>
-      <c r="G136" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H136" s="66"/>
+      <c r="C136" s="52"/>
+      <c r="D136" s="53"/>
+      <c r="E136" s="54"/>
+      <c r="F136" s="55"/>
+      <c r="G136" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H136" s="57"/>
     </row>
     <row r="137" spans="2:8">
-      <c r="B137" s="60" t="s">
+      <c r="B137" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="C137" s="61"/>
-      <c r="D137" s="62"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="64"/>
-      <c r="G137" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H137" s="66"/>
+      <c r="C137" s="52"/>
+      <c r="D137" s="53"/>
+      <c r="E137" s="54"/>
+      <c r="F137" s="55"/>
+      <c r="G137" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H137" s="57"/>
     </row>
     <row r="138" spans="2:8">
-      <c r="B138" s="60" t="s">
+      <c r="B138" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="C138" s="61"/>
-      <c r="D138" s="62"/>
-      <c r="E138" s="63"/>
-      <c r="F138" s="64"/>
-      <c r="G138" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H138" s="66"/>
+      <c r="C138" s="52"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="54"/>
+      <c r="F138" s="55"/>
+      <c r="G138" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H138" s="57"/>
     </row>
     <row r="139" spans="2:8">
-      <c r="B139" s="60" t="s">
+      <c r="B139" s="51" t="s">
         <v>147</v>
       </c>
-      <c r="C139" s="61"/>
-      <c r="D139" s="62"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="64"/>
-      <c r="G139" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H139" s="66"/>
+      <c r="C139" s="52"/>
+      <c r="D139" s="53"/>
+      <c r="E139" s="54"/>
+      <c r="F139" s="55"/>
+      <c r="G139" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H139" s="57"/>
     </row>
     <row r="140" spans="2:8">
-      <c r="B140" s="60" t="s">
+      <c r="B140" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="C140" s="61"/>
-      <c r="D140" s="62"/>
-      <c r="E140" s="63"/>
-      <c r="F140" s="64"/>
-      <c r="G140" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H140" s="66"/>
+      <c r="C140" s="52"/>
+      <c r="D140" s="53"/>
+      <c r="E140" s="54"/>
+      <c r="F140" s="55"/>
+      <c r="G140" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H140" s="57"/>
     </row>
     <row r="141" spans="2:8">
-      <c r="B141" s="60" t="s">
+      <c r="B141" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="C141" s="61"/>
-      <c r="D141" s="62"/>
-      <c r="E141" s="63"/>
-      <c r="F141" s="64"/>
-      <c r="G141" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H141" s="66"/>
+      <c r="C141" s="52"/>
+      <c r="D141" s="53"/>
+      <c r="E141" s="54"/>
+      <c r="F141" s="55"/>
+      <c r="G141" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H141" s="57"/>
     </row>
     <row r="142" spans="2:8">
-      <c r="B142" s="60" t="s">
+      <c r="B142" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="C142" s="61"/>
-      <c r="D142" s="62"/>
-      <c r="E142" s="63"/>
-      <c r="F142" s="64"/>
-      <c r="G142" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H142" s="66"/>
+      <c r="C142" s="52"/>
+      <c r="D142" s="53"/>
+      <c r="E142" s="54"/>
+      <c r="F142" s="55"/>
+      <c r="G142" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H142" s="57"/>
     </row>
     <row r="143" spans="2:8">
-      <c r="B143" s="60" t="s">
+      <c r="B143" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="C143" s="61"/>
-      <c r="D143" s="62"/>
-      <c r="E143" s="63"/>
-      <c r="F143" s="64"/>
-      <c r="G143" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H143" s="66"/>
+      <c r="C143" s="52"/>
+      <c r="D143" s="53"/>
+      <c r="E143" s="54"/>
+      <c r="F143" s="55"/>
+      <c r="G143" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H143" s="57"/>
     </row>
     <row r="144" spans="2:8">
-      <c r="B144" s="60" t="s">
+      <c r="B144" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="C144" s="61"/>
-      <c r="D144" s="62"/>
-      <c r="E144" s="63"/>
-      <c r="F144" s="64"/>
-      <c r="G144" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H144" s="66"/>
+      <c r="C144" s="52"/>
+      <c r="D144" s="53"/>
+      <c r="E144" s="54"/>
+      <c r="F144" s="55"/>
+      <c r="G144" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H144" s="57"/>
     </row>
     <row r="145" spans="2:8">
-      <c r="B145" s="60" t="s">
+      <c r="B145" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="C145" s="61"/>
-      <c r="D145" s="62"/>
-      <c r="E145" s="63"/>
-      <c r="F145" s="64"/>
-      <c r="G145" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H145" s="66"/>
+      <c r="C145" s="52"/>
+      <c r="D145" s="53"/>
+      <c r="E145" s="54"/>
+      <c r="F145" s="55"/>
+      <c r="G145" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H145" s="57"/>
     </row>
     <row r="146" spans="2:8">
-      <c r="B146" s="60" t="s">
+      <c r="B146" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="C146" s="61"/>
-      <c r="D146" s="62"/>
-      <c r="E146" s="63"/>
-      <c r="F146" s="64"/>
-      <c r="G146" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H146" s="66"/>
+      <c r="C146" s="52"/>
+      <c r="D146" s="53"/>
+      <c r="E146" s="54"/>
+      <c r="F146" s="55"/>
+      <c r="G146" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H146" s="57"/>
     </row>
     <row r="147" spans="2:8">
-      <c r="B147" s="60" t="s">
+      <c r="B147" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="C147" s="61"/>
-      <c r="D147" s="62"/>
-      <c r="E147" s="63"/>
-      <c r="F147" s="64"/>
-      <c r="G147" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H147" s="66"/>
+      <c r="C147" s="52"/>
+      <c r="D147" s="53"/>
+      <c r="E147" s="54"/>
+      <c r="F147" s="55"/>
+      <c r="G147" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H147" s="57"/>
     </row>
     <row r="148" spans="2:8">
-      <c r="B148" s="60" t="s">
+      <c r="B148" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="C148" s="61"/>
-      <c r="D148" s="62"/>
-      <c r="E148" s="63"/>
-      <c r="F148" s="64"/>
-      <c r="G148" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H148" s="66"/>
+      <c r="C148" s="52"/>
+      <c r="D148" s="53"/>
+      <c r="E148" s="54"/>
+      <c r="F148" s="55"/>
+      <c r="G148" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H148" s="57"/>
     </row>
     <row r="149" spans="2:8">
-      <c r="B149" s="60" t="s">
+      <c r="B149" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="C149" s="61"/>
-      <c r="D149" s="62"/>
-      <c r="E149" s="63"/>
-      <c r="F149" s="64"/>
-      <c r="G149" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H149" s="66"/>
+      <c r="C149" s="52"/>
+      <c r="D149" s="53"/>
+      <c r="E149" s="54"/>
+      <c r="F149" s="55"/>
+      <c r="G149" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H149" s="57"/>
     </row>
     <row r="150" spans="2:8">
-      <c r="B150" s="60" t="s">
+      <c r="B150" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="C150" s="61"/>
-      <c r="D150" s="62"/>
-      <c r="E150" s="63"/>
-      <c r="F150" s="64"/>
-      <c r="G150" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H150" s="66"/>
+      <c r="C150" s="52"/>
+      <c r="D150" s="53"/>
+      <c r="E150" s="54"/>
+      <c r="F150" s="55"/>
+      <c r="G150" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H150" s="57"/>
     </row>
     <row r="151" spans="2:8">
-      <c r="B151" s="60" t="s">
+      <c r="B151" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="C151" s="61"/>
-      <c r="D151" s="62"/>
-      <c r="E151" s="63"/>
-      <c r="F151" s="64"/>
-      <c r="G151" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H151" s="66"/>
+      <c r="C151" s="52"/>
+      <c r="D151" s="53"/>
+      <c r="E151" s="54"/>
+      <c r="F151" s="55"/>
+      <c r="G151" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H151" s="57"/>
     </row>
     <row r="152" spans="2:8">
-      <c r="B152" s="60" t="s">
+      <c r="B152" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="C152" s="61"/>
-      <c r="D152" s="62"/>
-      <c r="E152" s="63"/>
-      <c r="F152" s="64"/>
-      <c r="G152" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H152" s="66"/>
+      <c r="C152" s="52"/>
+      <c r="D152" s="53"/>
+      <c r="E152" s="54"/>
+      <c r="F152" s="55"/>
+      <c r="G152" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H152" s="57"/>
     </row>
     <row r="153" spans="2:8">
-      <c r="B153" s="60" t="s">
+      <c r="B153" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="C153" s="61"/>
-      <c r="D153" s="62"/>
-      <c r="E153" s="63"/>
-      <c r="F153" s="64"/>
-      <c r="G153" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H153" s="66"/>
+      <c r="C153" s="52"/>
+      <c r="D153" s="53"/>
+      <c r="E153" s="54"/>
+      <c r="F153" s="55"/>
+      <c r="G153" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H153" s="57"/>
     </row>
     <row r="154" spans="2:8">
-      <c r="B154" s="60" t="s">
+      <c r="B154" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="C154" s="61"/>
-      <c r="D154" s="62"/>
-      <c r="E154" s="63"/>
-      <c r="F154" s="64"/>
-      <c r="G154" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H154" s="66"/>
+      <c r="C154" s="52"/>
+      <c r="D154" s="53"/>
+      <c r="E154" s="54"/>
+      <c r="F154" s="55"/>
+      <c r="G154" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H154" s="57"/>
     </row>
     <row r="155" spans="2:8">
-      <c r="B155" s="60" t="s">
+      <c r="B155" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="C155" s="61"/>
-      <c r="D155" s="62"/>
-      <c r="E155" s="63"/>
-      <c r="F155" s="64"/>
-      <c r="G155" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H155" s="66"/>
+      <c r="C155" s="52"/>
+      <c r="D155" s="53"/>
+      <c r="E155" s="54"/>
+      <c r="F155" s="55"/>
+      <c r="G155" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H155" s="57"/>
     </row>
     <row r="156" spans="2:8">
-      <c r="B156" s="67" t="str">
+      <c r="B156" s="58" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,38,FALSE))</f>
         <v/>
       </c>
-      <c r="C156" s="68"/>
-      <c r="D156" s="69" t="str">
+      <c r="C156" s="59"/>
+      <c r="D156" s="60" t="str">
         <f>SUMPRODUCT(ROUND(D136:D155,2))</f>
         <v/>
       </c>
-      <c r="E156" s="69" t="str">
+      <c r="E156" s="60" t="str">
         <f>SUMPRODUCT(ROUND(E136:E155,2))</f>
         <v/>
       </c>
-      <c r="F156" s="69" t="str">
+      <c r="F156" s="60" t="str">
         <f>SUMPRODUCT(ROUND(F136:F155,2))</f>
         <v/>
       </c>
-      <c r="G156" s="70" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H156" s="71"/>
+      <c r="G156" s="61" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H156" s="62"/>
     </row>
     <row r="157" spans="2:8">
-      <c r="B157" s="55" t="s">
+      <c r="B157" s="46" t="s">
         <v>164</v>
       </c>
-      <c r="C157" s="72" t="str">
+      <c r="C157" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,39,FALSE))</f>
         <v/>
       </c>
-      <c r="D157" s="62"/>
-      <c r="E157" s="63"/>
-      <c r="F157" s="64"/>
-      <c r="G157" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H157" s="66"/>
+      <c r="D157" s="53"/>
+      <c r="E157" s="54"/>
+      <c r="F157" s="55"/>
+      <c r="G157" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H157" s="57"/>
     </row>
     <row r="158" spans="2:8">
-      <c r="B158" s="55" t="s">
+      <c r="B158" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="C158" s="72" t="str">
+      <c r="C158" s="63" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,40,FALSE))</f>
         <v/>
       </c>
-      <c r="D158" s="62"/>
-      <c r="E158" s="63"/>
-      <c r="F158" s="64"/>
-      <c r="G158" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H158" s="66"/>
+      <c r="D158" s="53"/>
+      <c r="E158" s="54"/>
+      <c r="F158" s="55"/>
+      <c r="G158" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H158" s="57"/>
     </row>
     <row r="159" spans="2:8">
-      <c r="B159" s="55" t="s">
+      <c r="B159" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="C159" s="73" t="str">
+      <c r="C159" s="64" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,41,FALSE))</f>
         <v/>
       </c>
-      <c r="D159" s="62"/>
-      <c r="E159" s="63"/>
-      <c r="F159" s="64"/>
-      <c r="G159" s="65" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H159" s="66"/>
+      <c r="D159" s="53"/>
+      <c r="E159" s="54"/>
+      <c r="F159" s="55"/>
+      <c r="G159" s="56" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H159" s="57"/>
     </row>
     <row r="160" spans="2:8">
-      <c r="B160" s="74" t="str">
+      <c r="B160" s="65" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,42,FALSE))</f>
         <v/>
       </c>
-      <c r="C160" s="75"/>
-      <c r="D160" s="76" t="str">
+      <c r="C160" s="66"/>
+      <c r="D160" s="67" t="str">
         <f>SUM(D48+D70+D102+D134+D156+D157+D158+D159)</f>
         <v/>
       </c>
-      <c r="E160" s="76" t="str">
+      <c r="E160" s="67" t="str">
         <f>SUM(E48+E70+E102+E134+E156+E157+E158+E159)</f>
         <v/>
       </c>
-      <c r="F160" s="76" t="str">
+      <c r="F160" s="67" t="str">
         <f>SUM(F48+F70+F102+F134+F156+F157+F158+F159)</f>
         <v/>
       </c>
-      <c r="G160" s="77" t="str">
-        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
-        <v/>
-      </c>
-      <c r="H160" s="78"/>
+      <c r="G160" s="68" t="str">
+        <f>IFERROR(INDEX($F$1:$F$1001,ROW())/INDEX($D$1:$D$1001,ROW()),0)</f>
+        <v/>
+      </c>
+      <c r="H160" s="69"/>
     </row>
     <row r="164" spans="2:5">
-      <c r="E164" s="80" t="str">
+      <c r="E164" s="71" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,44,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="165" spans="2:5">
-      <c r="B165" s="79" t="str">
+      <c r="B165" s="70" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,43,FALSE))</f>
         <v/>
       </c>
-      <c r="C165" s="79"/>
-      <c r="D165" s="79"/>
-      <c r="E165" s="80"/>
+      <c r="C165" s="70"/>
+      <c r="D165" s="70"/>
+      <c r="E165" s="71"/>
     </row>
     <row r="166" spans="2:5">
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="81"/>
-      <c r="E166" s="81" t="str">
+      <c r="B166" s="72"/>
+      <c r="C166" s="72"/>
+      <c r="D166" s="73"/>
+      <c r="E166" s="73" t="str">
         <f>B13</f>
         <v/>
       </c>
     </row>
     <row r="168" spans="2:5">
-      <c r="B168" s="56" t="str">
+      <c r="B168" s="47" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,45,FALSE))</f>
         <v/>
       </c>
-      <c r="C168" s="56"/>
-      <c r="D168" s="82" t="str">
+      <c r="C168" s="47"/>
+      <c r="D168" s="74" t="str">
         <f>IF(ROUND(E168;2)=ROUND(F20-F160;2);"✓";"")</f>
         <v/>
       </c>
-      <c r="E168" s="64" t="str">
+      <c r="E168" s="55" t="str">
         <f>E20-E160</f>
         <v/>
       </c>
     </row>
     <row r="170" spans="2:5">
-      <c r="B170" s="56" t="str">
+      <c r="B170" s="47" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,46,FALSE))</f>
         <v/>
       </c>
-      <c r="C170" s="56"/>
-      <c r="D170" s="56"/>
-      <c r="E170" s="83" t="str">
+      <c r="C170" s="47"/>
+      <c r="D170" s="47"/>
+      <c r="E170" s="75" t="str">
         <f>IF(E168=SUM(E170:E172);"OK";"")</f>
         <v/>
       </c>
     </row>
     <row r="171" spans="2:5">
-      <c r="B171" s="84" t="str">
+      <c r="B171" s="76" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,47,FALSE))</f>
         <v/>
       </c>
-      <c r="C171" s="84"/>
-      <c r="D171" s="84"/>
-      <c r="E171" s="64"/>
+      <c r="C171" s="76"/>
+      <c r="D171" s="76"/>
+      <c r="E171" s="55"/>
     </row>
     <row r="172" spans="2:5">
-      <c r="B172" s="84" t="str">
+      <c r="B172" s="76" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,48,FALSE))</f>
         <v/>
       </c>
-      <c r="C172" s="84"/>
-      <c r="D172" s="84"/>
-      <c r="E172" s="64"/>
+      <c r="C172" s="76"/>
+      <c r="D172" s="76"/>
+      <c r="E172" s="55"/>
     </row>
     <row r="173" spans="2:5">
-      <c r="B173" s="84" t="str">
+      <c r="B173" s="76" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,49,FALSE))</f>
         <v/>
       </c>
-      <c r="C173" s="84"/>
-      <c r="D173" s="84"/>
-      <c r="E173" s="64"/>
+      <c r="C173" s="76"/>
+      <c r="D173" s="76"/>
+      <c r="E173" s="55"/>
     </row>
     <row r="174" spans="2:5">
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
+      <c r="B174" s="72"/>
+      <c r="C174" s="72"/>
+      <c r="D174" s="72"/>
+      <c r="E174" s="72"/>
     </row>
     <row r="175" spans="2:5">
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
+      <c r="B175" s="72"/>
+      <c r="C175" s="72"/>
+      <c r="D175" s="72"/>
+      <c r="E175" s="72"/>
     </row>
     <row r="176" spans="2:5">
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
+      <c r="B176" s="72"/>
+      <c r="C176" s="72"/>
+      <c r="D176" s="72"/>
+      <c r="E176" s="72"/>
     </row>
     <row r="177" spans="2:5">
-      <c r="B177" s="6" t="str">
+      <c r="B177" s="72" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,50,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="178" spans="2:5">
-      <c r="B178" s="6" t="str">
+      <c r="B178" s="72" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,54,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="179" spans="2:5">
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
+      <c r="B179" s="72"/>
+      <c r="C179" s="72"/>
+      <c r="D179" s="72"/>
+      <c r="E179" s="72"/>
     </row>
     <row r="180" spans="2:5">
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
+      <c r="B180" s="72"/>
+      <c r="C180" s="72"/>
+      <c r="D180" s="72"/>
+      <c r="E180" s="72"/>
     </row>
     <row r="181" spans="2:5">
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
+      <c r="B181" s="72"/>
+      <c r="C181" s="72"/>
+      <c r="D181" s="72"/>
+      <c r="E181" s="72"/>
     </row>
     <row r="182" spans="2:5">
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
+      <c r="B182" s="72"/>
+      <c r="C182" s="72"/>
+      <c r="D182" s="72"/>
+      <c r="E182" s="72"/>
     </row>
     <row r="183" spans="2:5">
-      <c r="B183" s="85" t="str">
+      <c r="B183" s="77" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,51,FALSE))</f>
         <v/>
       </c>
-      <c r="C183" s="6"/>
-      <c r="D183" s="85" t="str">
+      <c r="C183" s="72"/>
+      <c r="D183" s="77" t="str">
         <f>IF($E$2="","",VLOOKUP($E$2,Sprachversionen!$B:$BN,52,FALSE))</f>
         <v/>
       </c>
-      <c r="E183" s="6"/>
+      <c r="E183" s="72"/>
     </row>
     <row r="184" spans="2:5">
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
+      <c r="B184" s="72"/>
+      <c r="C184" s="72"/>
+      <c r="D184" s="72"/>
+      <c r="E184" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -5906,13 +5792,13 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="G9:H9"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="Q11:R11"/>
     <mergeCell ref="D11:D14"/>
     <mergeCell ref="E11:E14"/>
     <mergeCell ref="F11:F14"/>
     <mergeCell ref="G11:G14"/>
     <mergeCell ref="H11:H14"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="Q11:R11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B15:C15"/>
